--- a/AT/GearListNew.xlsx
+++ b/AT/GearListNew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1087" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24D85728-79F7-4777-BE3C-8121193D70E1}"/>
+  <xr:revisionPtr revIDLastSave="1108" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333B2FE3-6D6B-4859-95EB-739BE215FF09}"/>
   <bookViews>
-    <workbookView xWindow="-21600" yWindow="1035" windowWidth="21600" windowHeight="14475" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
+    <workbookView xWindow="1590" yWindow="1005" windowWidth="27210" windowHeight="15195" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gear Checklist" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="265">
   <si>
     <t>gm</t>
   </si>
@@ -334,9 +334,6 @@
   </si>
   <si>
     <t>Fleece hat</t>
-  </si>
-  <si>
-    <t>Under Quilt</t>
   </si>
   <si>
     <t>Kitchen Group</t>
@@ -786,9 +783,6 @@
     <t>Tyvek 8x3 footprint</t>
   </si>
   <si>
-    <t>New Hammock; 1.6oz Hexon</t>
-  </si>
-  <si>
     <t>Spreader Bars 28"</t>
   </si>
   <si>
@@ -940,6 +934,12 @@
   </si>
   <si>
     <t>Selected Items Weight for base pack weight</t>
+  </si>
+  <si>
+    <t>Under Quilt Blue 5.0 Climashield</t>
+  </si>
+  <si>
+    <t>get dimensions</t>
   </si>
 </sst>
 </file>
@@ -1638,44 +1638,30 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{11F929FC-84B5-425F-A422-9C245DCEA07D}"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="9">
     <dxf>
       <font>
-        <color auto="1"/>
+        <b/>
+        <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1715,61 +1701,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1795,9 +1726,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1835,7 +1766,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1941,7 +1872,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2083,7 +2014,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2126,7 +2057,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F1" s="40" t="s">
         <v>78</v>
@@ -2152,16 +2083,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L2" s="26"/>
       <c r="M2" s="35"/>
@@ -2191,22 +2122,22 @@
         <v>0</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="72" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K3" s="26"/>
       <c r="L3" s="26"/>
       <c r="M3" s="35"/>
       <c r="N3" s="27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O3" s="26"/>
       <c r="P3" s="26"/>
@@ -2217,7 +2148,7 @@
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>42</v>
@@ -2249,7 +2180,7 @@
         <v>13.50344803259317</v>
       </c>
       <c r="J4" s="73" t="str" cm="1">
-        <f t="array" ref="J4:J14">_xlfn._xlws.FILTER(E4:E206,"x"=K4:K206)</f>
+        <f t="array" ref="J4:J13">_xlfn._xlws.FILTER(E4:E206,"x"=K4:K206)</f>
         <v>New Pack</v>
       </c>
       <c r="K4" s="20"/>
@@ -2354,7 +2285,7 @@
         <v>8.2188398384451222</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O6" s="25"/>
       <c r="P6" s="25"/>
@@ -2391,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="74" t="str">
-        <v>New Hammock; 1.6oz Hexon</v>
+        <v>bug net new</v>
       </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
@@ -2437,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="74" t="str">
-        <v>bug net new</v>
+        <v>sleeping bag liner #2</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
@@ -2446,7 +2377,7 @@
         <v>44.797968218134358</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O8" s="25"/>
       <c r="P8" s="25"/>
@@ -2457,7 +2388,7 @@
     </row>
     <row r="9" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>42</v>
@@ -2489,16 +2420,16 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="J9" s="74" t="str">
-        <v>sleeping bag liner #2</v>
+        <v>Top Quilt</v>
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
-      <c r="M9" s="21">
+      <c r="M9" s="21" t="str">
         <f>VLOOKUP(N9,E46:G47,3,FALSE)</f>
-        <v>6.2082223672375179</v>
+        <v/>
       </c>
       <c r="N9" s="25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O9" s="25"/>
       <c r="P9" s="25"/>
@@ -2509,7 +2440,7 @@
     </row>
     <row r="10" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>42</v>
@@ -2541,7 +2472,7 @@
         <v>5.0441806733804828</v>
       </c>
       <c r="J10" s="74" t="str">
-        <v>Top Quilt</v>
+        <v>New Under Quilt</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
@@ -2583,7 +2514,7 @@
         <v>7.0547981445880881</v>
       </c>
       <c r="J11" s="74" t="str">
-        <v>New Under Quilt</v>
+        <v>New Rain Pants Xeon</v>
       </c>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
@@ -2598,7 +2529,7 @@
     </row>
     <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>42</v>
@@ -2630,7 +2561,7 @@
         <v>5.1500026455493044</v>
       </c>
       <c r="J12" s="74" t="str">
-        <v>New Rain Pants Xeon</v>
+        <v>BRS 3000T Stove</v>
       </c>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
@@ -2651,7 +2582,7 @@
         <v/>
       </c>
       <c r="E13" s="31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F13" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2670,7 +2601,7 @@
         <v/>
       </c>
       <c r="J13" s="74" t="str">
-        <v>BRS 3000T Stove</v>
+        <v>Ultralight chair</v>
       </c>
       <c r="K13" s="20" t="s">
         <v>42</v>
@@ -2716,9 +2647,7 @@
         <f t="shared" si="4"/>
         <v>8.6500291010423496</v>
       </c>
-      <c r="J14" s="74" t="str">
-        <v>Ultralight chair</v>
-      </c>
+      <c r="J14" s="74"/>
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
       <c r="M14" s="21"/>
@@ -2780,7 +2709,7 @@
         <v>13.545212437609129</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F16" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2812,7 +2741,7 @@
     </row>
     <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>42</v>
@@ -2825,7 +2754,7 @@
         <v>8.2188398384451222</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F17" s="20">
         <f t="shared" si="1"/>
@@ -2863,7 +2792,7 @@
         <v/>
       </c>
       <c r="E18" s="114" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F18" s="20" t="str">
         <f t="shared" ref="F18:F19" si="6">IF(B18="x",IF(C18=0,"",C18),"")</f>
@@ -2902,9 +2831,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E19" s="83" t="s">
-        <v>213</v>
-      </c>
+      <c r="E19" s="83"/>
       <c r="F19" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2922,9 +2849,7 @@
         <v/>
       </c>
       <c r="J19" s="25"/>
-      <c r="K19" s="20" t="s">
-        <v>42</v>
-      </c>
+      <c r="K19" s="20"/>
       <c r="L19" s="20"/>
       <c r="M19" s="21"/>
       <c r="N19" s="25"/>
@@ -2937,7 +2862,7 @@
     </row>
     <row r="20" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>42</v>
@@ -2950,7 +2875,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F20" s="20">
         <f t="shared" ref="F20:F21" si="10">IF(B20="x",IF(C20=0,"",C20),"")</f>
@@ -2989,7 +2914,7 @@
         <v>7.9719219033845397</v>
       </c>
       <c r="E21" s="80" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F21" s="20" t="str">
         <f t="shared" si="10"/>
@@ -3061,7 +2986,7 @@
     </row>
     <row r="23" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>42</v>
@@ -3074,7 +2999,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F23" s="20">
         <f t="shared" si="1"/>
@@ -3093,7 +3018,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -3148,7 +3073,7 @@
     </row>
     <row r="25" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>42</v>
@@ -3161,7 +3086,7 @@
         <v>1.4109596289176176</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F25" s="20">
         <f t="shared" si="1"/>
@@ -3233,7 +3158,7 @@
     </row>
     <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>42</v>
@@ -3246,7 +3171,7 @@
         <v>16.71987160267377</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F27" s="20">
         <v>300</v>
@@ -3264,7 +3189,7 @@
         <v>0.71987160267376993</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
@@ -3279,7 +3204,7 @@
     </row>
     <row r="28" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>42</v>
@@ -3364,7 +3289,7 @@
     </row>
     <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C30" s="56">
         <v>126</v>
@@ -3406,7 +3331,7 @@
     </row>
     <row r="31" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C31" s="56">
         <v>311</v>
@@ -3448,7 +3373,7 @@
     </row>
     <row r="32" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C32" s="56">
         <v>0</v>
@@ -3477,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>42</v>
@@ -3494,7 +3419,7 @@
     </row>
     <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C33" s="56">
         <v>545</v>
@@ -3536,7 +3461,7 @@
     </row>
     <row r="34" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C34" s="56">
         <v>305</v>
@@ -3620,7 +3545,7 @@
     </row>
     <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="56">
@@ -3631,7 +3556,7 @@
         <v>4.1976048960299126</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F36" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3671,7 +3596,7 @@
         <v>6.878428190973386</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F37" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3916,7 +3841,7 @@
         <v>44.797968218134358</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F43" s="20">
         <f t="shared" si="1"/>
@@ -3956,7 +3881,7 @@
         <v>55.203795481401791</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F44" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3996,7 +3921,7 @@
         <v>38.413375897282137</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" s="20" t="str">
         <f t="shared" ref="F45" si="12">IF(B45="x",IF(C45=0,"",C45),"")</f>
@@ -4038,7 +3963,7 @@
         <v>6.2082223672375179</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" s="20">
         <f t="shared" si="1"/>
@@ -4077,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F47" s="20" t="str">
         <f t="shared" ref="F47" si="14">IF(B47="x",IF(C47=0,"",C47),"")</f>
@@ -4096,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>42</v>
@@ -4121,7 +4046,7 @@
         <v>3.033563202172878</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F48" s="20" t="str">
         <f t="shared" ref="F48" si="17">IF(B48="x",IF(C48=0,"",C48),"")</f>
@@ -4163,7 +4088,7 @@
         <v>3.1746591650646399</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="20">
         <f t="shared" ref="F49" si="19">IF(B49="x",IF(C49=0,"",C49),"")</f>
@@ -4234,7 +4159,7 @@
     </row>
     <row r="51" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="56">
@@ -4281,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F52" s="20" t="str">
         <f t="shared" ref="F52" si="21">IF(B52="x",IF(C52=0,"",C52),"")</f>
@@ -4325,7 +4250,7 @@
         <v>31.676043669200517</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="F53" s="20">
         <f t="shared" si="1"/>
@@ -4343,7 +4268,9 @@
         <f t="shared" si="4"/>
         <v>15.676043669200517</v>
       </c>
-      <c r="J53" s="25"/>
+      <c r="J53" s="25" t="s">
+        <v>264</v>
+      </c>
       <c r="K53" s="20"/>
       <c r="L53" s="20"/>
       <c r="M53" s="21"/>
@@ -4359,7 +4286,7 @@
       <c r="C54" s="56"/>
       <c r="D54" s="21"/>
       <c r="E54" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="21"/>
@@ -4432,7 +4359,7 @@
         <v/>
       </c>
       <c r="E56" s="27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F56" s="20" t="str">
         <f t="shared" si="23"/>
@@ -4474,7 +4401,7 @@
         <v>2.9630152207269971</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F57" s="20">
         <f t="shared" si="23"/>
@@ -4555,7 +4482,7 @@
         <v>1.0934937124111537</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F59" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4594,7 +4521,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F60" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4636,7 +4563,7 @@
         <v>5.2205506269951849</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="20">
         <f t="shared" si="1"/>
@@ -4759,7 +4686,7 @@
         <v>5.8554824600081128</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="1"/>
@@ -4801,7 +4728,7 @@
         <v>1.6578775639782006</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" ref="F65" si="25">IF(B65="x",IF(C65=0,"",C65),"")</f>
@@ -4963,7 +4890,7 @@
         <v>13.580486428332069</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="27"/>
@@ -5046,7 +4973,7 @@
         <v/>
       </c>
       <c r="E71" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F71" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5088,7 +5015,7 @@
         <v>8.6068537363974684</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72" s="14">
         <f t="shared" si="27"/>
@@ -5128,7 +5055,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F73" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5147,7 +5074,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K73" s="20"/>
       <c r="L73" s="20"/>
@@ -5170,7 +5097,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="E74" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F74" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5189,7 +5116,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -5212,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F75" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5254,7 +5181,7 @@
         <v>4.5503448032593168</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F76" s="14">
         <f t="shared" ref="F76" si="33">IF(B76="x",IF(C76=0,"",C76),"")</f>
@@ -5293,7 +5220,7 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="E77" s="46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F77" s="14" t="str">
         <f t="shared" ref="F77" si="35">IF(B77="x",IF(C77=0,"",C77),"")</f>
@@ -5312,7 +5239,7 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K77" s="20" t="s">
         <v>42</v>
@@ -5420,7 +5347,7 @@
         <v/>
       </c>
       <c r="E80" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F80" s="14" t="str">
         <f t="shared" ref="F80:F151" si="37">IF(B80="x",IF(C80=0,"",C80),"")</f>
@@ -5439,7 +5366,7 @@
         <v/>
       </c>
       <c r="J80" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K80" s="20"/>
       <c r="L80" s="20"/>
@@ -5461,7 +5388,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F81" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5503,7 +5430,7 @@
         <v>2.7513712763893543</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F82" s="14">
         <f t="shared" si="37"/>
@@ -5545,7 +5472,7 @@
         <v>3.8801389795234487</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F83" s="14">
         <f t="shared" si="37"/>
@@ -5585,7 +5512,7 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="E84" s="46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F84" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5604,7 +5531,7 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="J84" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K84" s="20" t="s">
         <v>42</v>
@@ -5629,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F85" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5671,7 +5598,7 @@
         <v>8.0071958941074808</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F86" s="14">
         <f t="shared" si="37"/>
@@ -5711,7 +5638,7 @@
         <v>4.0212349424152105</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F87" s="14" t="str">
         <f t="shared" ref="F87" si="40">IF(B87="x",IF(C87=0,"",C87),"")</f>
@@ -5751,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F88" s="14" t="str">
         <f t="shared" ref="F88:F97" si="42">IF(B88="x",IF(C88=0,"",C88),"")</f>
@@ -5793,7 +5720,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F89" s="14">
         <f t="shared" si="42"/>
@@ -5835,7 +5762,7 @@
         <v>0.91712375879645147</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F90" s="14">
         <f t="shared" si="42"/>
@@ -5877,7 +5804,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F91" s="14">
         <f t="shared" si="42"/>
@@ -5917,7 +5844,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F92" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5957,7 +5884,7 @@
         <v>0.4938358701211662</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F93" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5999,7 +5926,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F94" s="14">
         <f t="shared" si="42"/>
@@ -6041,7 +5968,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F95" s="14">
         <f t="shared" si="42"/>
@@ -6083,7 +6010,7 @@
         <v>7.372264061094552</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F96" s="14">
         <f t="shared" si="42"/>
@@ -6125,7 +6052,7 @@
         <v>1.2345896753029155</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F97" s="14">
         <f t="shared" si="42"/>
@@ -6167,7 +6094,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F98" s="14">
         <f t="shared" ref="F98" si="44">IF(B98="x",IF(C98=0,"",C98),"")</f>
@@ -6249,7 +6176,7 @@
         <v/>
       </c>
       <c r="E100" s="48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F100" s="14"/>
       <c r="G100" s="81"/>
@@ -6262,7 +6189,7 @@
         <v/>
       </c>
       <c r="J100" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -6285,7 +6212,7 @@
         <v/>
       </c>
       <c r="E101" s="48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F101" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6325,7 +6252,7 @@
         <v/>
       </c>
       <c r="E102" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F102" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6365,7 +6292,7 @@
         <v/>
       </c>
       <c r="E103" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F103" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6405,7 +6332,7 @@
         <v/>
       </c>
       <c r="E104" s="48" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F104" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6436,7 +6363,7 @@
       <c r="T104" s="20"/>
     </row>
     <row r="105" spans="2:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="B105" s="18"/>
+      <c r="B105" s="124"/>
       <c r="C105" s="56">
         <v>46</v>
       </c>
@@ -6445,7 +6372,7 @@
         <v>1.6226035732552604</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F105" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6482,22 +6409,28 @@
       <c r="C106" s="56">
         <v>41</v>
       </c>
-      <c r="D106" s="21"/>
+      <c r="D106" s="21">
+        <f t="shared" si="48"/>
+        <v>1.4462336196405581</v>
+      </c>
       <c r="E106" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F106" s="14">
         <f t="shared" si="37"/>
         <v>41</v>
       </c>
-      <c r="G106" s="81"/>
+      <c r="G106" s="81">
+        <f t="shared" ref="G106" si="49">IF(B106="x",D106,"")</f>
+        <v>1.4462336196405581</v>
+      </c>
       <c r="H106" s="89">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="21" t="str">
-        <f t="shared" si="32"/>
-        <v/>
+        <f t="shared" ref="H106" si="50">IF(C106="","",INT(D106/16))</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="21">
+        <f t="shared" ref="I106" si="51">IF(D106="","",MOD(D106,16))</f>
+        <v>1.4462336196405581</v>
       </c>
       <c r="J106" s="25"/>
       <c r="K106" s="20"/>
@@ -6683,7 +6616,7 @@
         <v/>
       </c>
       <c r="E111" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F111" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6765,7 +6698,7 @@
         <v/>
       </c>
       <c r="E113" s="53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F113" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6805,7 +6738,7 @@
         <v/>
       </c>
       <c r="E114" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F114" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6840,7 +6773,7 @@
         <v/>
       </c>
       <c r="E115" s="54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F115" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6874,7 +6807,7 @@
         <v/>
       </c>
       <c r="E116" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F116" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6908,7 +6841,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F117" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6944,7 +6877,7 @@
         <v>1.8342475175929029</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F118" s="14">
         <f t="shared" si="37"/>
@@ -6976,7 +6909,7 @@
         <v>0.74075380518174927</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F119" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7008,7 +6941,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F120" s="14">
         <f t="shared" si="37"/>
@@ -7072,7 +7005,7 @@
         <v>0.77602779590468973</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F122" s="14">
         <f t="shared" si="37"/>
@@ -7102,7 +7035,7 @@
         <v>2.1517134340993671</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F123" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7134,7 +7067,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F124" s="14">
         <f t="shared" si="37"/>
@@ -7197,7 +7130,7 @@
         <v/>
       </c>
       <c r="E126" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F126" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7259,7 +7192,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F128" s="14">
         <f t="shared" si="37"/>
@@ -7416,7 +7349,7 @@
         <v/>
       </c>
       <c r="E133" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F133" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7444,11 +7377,11 @@
         <v>160</v>
       </c>
       <c r="D134" s="21">
-        <f t="shared" ref="D134:D162" si="49">IF(ISBLANK(C134),"", C134/$D$211)</f>
+        <f t="shared" ref="D134:D162" si="52">IF(ISBLANK(C134),"", C134/$D$211)</f>
         <v>5.6438385156704705</v>
       </c>
       <c r="E134" s="66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F134" s="14">
         <f t="shared" si="37"/>
@@ -7472,11 +7405,11 @@
       <c r="B135" s="18"/>
       <c r="C135" s="56"/>
       <c r="D135" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E135" s="66" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F135" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7487,11 +7420,11 @@
         <v/>
       </c>
       <c r="H135" s="89" t="str">
-        <f t="shared" ref="H135:H178" si="50">IF(C135="","",INT(D135/16))</f>
+        <f t="shared" ref="H135:H178" si="53">IF(C135="","",INT(D135/16))</f>
         <v/>
       </c>
       <c r="I135" s="21" t="str">
-        <f t="shared" ref="I135:I178" si="51">IF(D135="","",MOD(D135,16))</f>
+        <f t="shared" ref="I135:I178" si="54">IF(D135="","",MOD(D135,16))</f>
         <v/>
       </c>
       <c r="J135" s="25"/>
@@ -7500,11 +7433,11 @@
       <c r="B136" s="18"/>
       <c r="C136" s="56"/>
       <c r="D136" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E136" s="66" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F136" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7515,11 +7448,11 @@
         <v/>
       </c>
       <c r="H136" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I136" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J136" s="25"/>
@@ -7530,7 +7463,7 @@
       </c>
       <c r="C137" s="56"/>
       <c r="D137" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E137" s="25" t="s">
@@ -7545,11 +7478,11 @@
         <v/>
       </c>
       <c r="H137" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I137" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J137" s="25"/>
@@ -7560,11 +7493,11 @@
       </c>
       <c r="C138" s="56"/>
       <c r="D138" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E138" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F138" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7575,11 +7508,11 @@
         <v/>
       </c>
       <c r="H138" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I138" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J138" s="25"/>
@@ -7592,11 +7525,11 @@
         <v>12</v>
       </c>
       <c r="D139" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.42328788867528527</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F139" s="14">
         <f t="shared" si="37"/>
@@ -7607,11 +7540,11 @@
         <v>0.42328788867528527</v>
       </c>
       <c r="H139" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I139" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0.42328788867528527</v>
       </c>
       <c r="J139" s="25"/>
@@ -7622,11 +7555,11 @@
       </c>
       <c r="C140" s="56"/>
       <c r="D140" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E140" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F140" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7637,11 +7570,11 @@
         <v/>
       </c>
       <c r="H140" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I140" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J140" s="25"/>
@@ -7654,11 +7587,11 @@
         <v>38</v>
       </c>
       <c r="D141" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.3404116474717367</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F141" s="14">
         <f t="shared" si="37"/>
@@ -7669,11 +7602,11 @@
         <v>1.3404116474717367</v>
       </c>
       <c r="H141" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I141" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.3404116474717367</v>
       </c>
       <c r="J141" s="25"/>
@@ -7687,7 +7620,7 @@
         <v>50</v>
       </c>
       <c r="D142" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.763699536147022</v>
       </c>
       <c r="E142" s="25" t="s">
@@ -7702,11 +7635,11 @@
         <v>1.763699536147022</v>
       </c>
       <c r="H142" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I142" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.763699536147022</v>
       </c>
       <c r="J142" s="25"/>
@@ -7717,11 +7650,11 @@
       </c>
       <c r="C143" s="56"/>
       <c r="D143" s="21" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v/>
       </c>
       <c r="E143" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F143" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7732,11 +7665,11 @@
         <v/>
       </c>
       <c r="H143" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I143" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J143" s="56"/>
@@ -7751,11 +7684,11 @@
         <v>185</v>
       </c>
       <c r="D144" s="57">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>6.5256882837439818</v>
       </c>
       <c r="E144" s="58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F144" s="58" t="str">
         <f t="shared" si="37"/>
@@ -7766,11 +7699,11 @@
         <v/>
       </c>
       <c r="H144" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I144" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>6.5256882837439818</v>
       </c>
       <c r="J144" s="25"/>
@@ -7783,26 +7716,26 @@
         <v>135</v>
       </c>
       <c r="D145" s="57">
-        <f t="shared" ref="D145" si="52">IF(ISBLANK(C145),"", C145/$D$211)</f>
+        <f t="shared" ref="D145" si="55">IF(ISBLANK(C145),"", C145/$D$211)</f>
         <v>4.7619887475969591</v>
       </c>
       <c r="E145" s="58" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F145" s="58">
-        <f t="shared" ref="F145" si="53">IF(B145="x",IF(C145=0,"",C145),"")</f>
+        <f t="shared" ref="F145" si="56">IF(B145="x",IF(C145=0,"",C145),"")</f>
         <v>135</v>
       </c>
       <c r="G145" s="82">
-        <f t="shared" ref="G145" si="54">IF(B145="x",D145,"")</f>
+        <f t="shared" ref="G145" si="57">IF(B145="x",D145,"")</f>
         <v>4.7619887475969591</v>
       </c>
       <c r="H145" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I145" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4.7619887475969591</v>
       </c>
       <c r="J145" s="25"/>
@@ -7813,7 +7746,7 @@
         <v>480</v>
       </c>
       <c r="D146" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>16.931515547011411</v>
       </c>
       <c r="E146" s="50" t="s">
@@ -7828,11 +7761,11 @@
         <v/>
       </c>
       <c r="H146" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="I146" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0.93151554701141137</v>
       </c>
       <c r="J146" s="25"/>
@@ -7843,7 +7776,7 @@
         <v>510</v>
       </c>
       <c r="D147" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>17.989735268699626</v>
       </c>
       <c r="E147" s="61" t="s">
@@ -7858,15 +7791,15 @@
         <v/>
       </c>
       <c r="H147" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>1</v>
       </c>
       <c r="I147" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.9897352686996257</v>
       </c>
       <c r="J147" s="67" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K147" s="19" t="s">
         <v>42</v>
@@ -7880,11 +7813,11 @@
         <v>1000</v>
       </c>
       <c r="D148" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>35.273990722940439</v>
       </c>
       <c r="E148" s="58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F148" s="14">
         <f t="shared" si="37"/>
@@ -7895,11 +7828,11 @@
         <v>35.273990722940439</v>
       </c>
       <c r="H148" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>2</v>
       </c>
       <c r="I148" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.2739907229404395</v>
       </c>
       <c r="J148" s="67"/>
@@ -7912,11 +7845,11 @@
         <v>131</v>
       </c>
       <c r="D149" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>4.6208927847051982</v>
       </c>
       <c r="E149" s="50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F149" s="14">
         <f t="shared" si="37"/>
@@ -7927,11 +7860,11 @@
         <v>4.6208927847051982</v>
       </c>
       <c r="H149" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I149" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4.6208927847051982</v>
       </c>
       <c r="J149" s="25"/>
@@ -7945,7 +7878,7 @@
         <v>69</v>
       </c>
       <c r="D150" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>2.4339053598828904</v>
       </c>
       <c r="E150" s="14" t="s">
@@ -7960,11 +7893,11 @@
         <v>2.4339053598828904</v>
       </c>
       <c r="H150" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I150" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>2.4339053598828904</v>
       </c>
       <c r="J150" s="25"/>
@@ -7975,11 +7908,11 @@
         <v>0</v>
       </c>
       <c r="D151" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F151" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7990,11 +7923,11 @@
         <v/>
       </c>
       <c r="H151" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I151" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J151" s="25"/>
@@ -8007,26 +7940,26 @@
         <v>36</v>
       </c>
       <c r="D152" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.269863666025856</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F152" s="14">
-        <f t="shared" ref="F152:F162" si="55">IF(B152="x",IF(C152=0,"",C152),"")</f>
+        <f t="shared" ref="F152:F162" si="58">IF(B152="x",IF(C152=0,"",C152),"")</f>
         <v>36</v>
       </c>
       <c r="G152" s="81">
-        <f t="shared" ref="G152:G162" si="56">IF(B152="x",D152,"")</f>
+        <f t="shared" ref="G152:G162" si="59">IF(B152="x",D152,"")</f>
         <v>1.269863666025856</v>
       </c>
       <c r="H152" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I152" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.269863666025856</v>
       </c>
       <c r="J152" s="25"/>
@@ -8039,26 +7972,26 @@
         <v>72</v>
       </c>
       <c r="D153" s="21">
-        <f t="shared" ref="D153" si="57">IF(ISBLANK(C153),"", C153/$D$211)</f>
+        <f t="shared" ref="D153" si="60">IF(ISBLANK(C153),"", C153/$D$211)</f>
         <v>2.539727332051712</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F153" s="14" t="str">
-        <f t="shared" ref="F153" si="58">IF(B153="x",IF(C153=0,"",C153),"")</f>
+        <f t="shared" ref="F153" si="61">IF(B153="x",IF(C153=0,"",C153),"")</f>
         <v/>
       </c>
       <c r="G153" s="81" t="str">
-        <f t="shared" ref="G153" si="59">IF(B153="x",D153,"")</f>
+        <f t="shared" ref="G153" si="62">IF(B153="x",D153,"")</f>
         <v/>
       </c>
       <c r="H153" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I153" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>2.539727332051712</v>
       </c>
       <c r="J153" s="25"/>
@@ -8070,26 +8003,26 @@
         <v>30</v>
       </c>
       <c r="D154" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.0582197216882132</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F154" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G154" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H154" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I154" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.0582197216882132</v>
       </c>
       <c r="J154" s="25"/>
@@ -8102,26 +8035,26 @@
         <v>30</v>
       </c>
       <c r="D155" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.0582197216882132</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>17</v>
       </c>
       <c r="F155" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>30</v>
       </c>
       <c r="G155" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1.0582197216882132</v>
       </c>
       <c r="H155" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I155" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.0582197216882132</v>
       </c>
     </row>
@@ -8133,26 +8066,26 @@
         <v>20</v>
       </c>
       <c r="D156" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0.70547981445880881</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F156" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>20</v>
       </c>
       <c r="G156" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.70547981445880881</v>
       </c>
       <c r="H156" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I156" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0.70547981445880881</v>
       </c>
       <c r="J156" s="25"/>
@@ -8164,26 +8097,26 @@
         <v>0</v>
       </c>
       <c r="D157" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F157" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G157" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H157" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I157" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J157" s="25"/>
@@ -8195,26 +8128,26 @@
         <v>0</v>
       </c>
       <c r="D158" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>45</v>
       </c>
       <c r="F158" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G158" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H158" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I158" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J158" s="25"/>
@@ -8226,26 +8159,26 @@
         <v>0</v>
       </c>
       <c r="D159" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E159" s="25" t="s">
         <v>51</v>
       </c>
       <c r="F159" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G159" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H159" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I159" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J159" s="25"/>
@@ -8256,26 +8189,26 @@
         <v>0</v>
       </c>
       <c r="D160" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F160" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G160" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H160" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I160" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J160" s="25"/>
@@ -8289,26 +8222,26 @@
         <v>49</v>
       </c>
       <c r="D161" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>1.7284255454240816</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F161" s="14">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v>49</v>
       </c>
       <c r="G161" s="81">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>1.7284255454240816</v>
       </c>
       <c r="H161" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I161" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.7284255454240816</v>
       </c>
       <c r="J161" s="25"/>
@@ -8319,26 +8252,26 @@
         <v>94</v>
       </c>
       <c r="D162" s="21">
-        <f t="shared" si="49"/>
+        <f t="shared" si="52"/>
         <v>3.3157551279564013</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F162" s="14" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="58"/>
         <v/>
       </c>
       <c r="G162" s="81" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v/>
       </c>
       <c r="H162" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I162" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.3157551279564013</v>
       </c>
       <c r="J162" s="25"/>
@@ -8349,26 +8282,26 @@
         <v>88</v>
       </c>
       <c r="D163" s="21">
-        <f t="shared" ref="D163:D206" si="60">IF(ISBLANK(C163),"", C163/$D$211)</f>
+        <f t="shared" ref="D163:D206" si="63">IF(ISBLANK(C163),"", C163/$D$211)</f>
         <v>3.1041111836187589</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F163" s="14" t="str">
-        <f t="shared" ref="F163:F206" si="61">IF(B163="x",IF(C163=0,"",C163),"")</f>
+        <f t="shared" ref="F163:F206" si="64">IF(B163="x",IF(C163=0,"",C163),"")</f>
         <v/>
       </c>
       <c r="G163" s="81" t="str">
-        <f t="shared" ref="G163:G207" si="62">IF(B163="x",D163,"")</f>
+        <f t="shared" ref="G163:G207" si="65">IF(B163="x",D163,"")</f>
         <v/>
       </c>
       <c r="H163" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I163" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.1041111836187589</v>
       </c>
       <c r="J163" s="25"/>
@@ -8386,26 +8319,26 @@
         <v>1886</v>
       </c>
       <c r="D164" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>66.526746503465674</v>
       </c>
       <c r="E164" s="25" t="s">
         <v>41</v>
       </c>
       <c r="F164" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>1886</v>
       </c>
       <c r="G164" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>66.526746503465674</v>
       </c>
       <c r="H164" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>4</v>
       </c>
       <c r="I164" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>2.5267465034656738</v>
       </c>
       <c r="J164" s="25"/>
@@ -8420,26 +8353,26 @@
       </c>
       <c r="C165" s="56"/>
       <c r="D165" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E165" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F165" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G165" s="81" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H165" s="89" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I165" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J165" s="25"/>
@@ -8456,26 +8389,26 @@
         <v>322</v>
       </c>
       <c r="D166" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>11.358225012786821</v>
       </c>
       <c r="E166" s="25" t="s">
         <v>26</v>
       </c>
       <c r="F166" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>322</v>
       </c>
       <c r="G166" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>11.358225012786821</v>
       </c>
       <c r="H166" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I166" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>11.358225012786821</v>
       </c>
       <c r="J166" s="25"/>
@@ -8492,26 +8425,26 @@
         <v>108</v>
       </c>
       <c r="D167" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>3.8095909980775677</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F167" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>108</v>
       </c>
       <c r="G167" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>3.8095909980775677</v>
       </c>
       <c r="H167" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I167" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>3.8095909980775677</v>
       </c>
       <c r="J167" s="25"/>
@@ -8526,26 +8459,26 @@
         <v>36</v>
       </c>
       <c r="D168" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1.269863666025856</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F168" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G168" s="81" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H168" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I168" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.269863666025856</v>
       </c>
       <c r="J168" s="25"/>
@@ -8562,26 +8495,26 @@
         <v>50</v>
       </c>
       <c r="D169" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>1.763699536147022</v>
       </c>
       <c r="E169" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F169" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>50</v>
       </c>
       <c r="G169" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>1.763699536147022</v>
       </c>
       <c r="H169" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I169" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>1.763699536147022</v>
       </c>
       <c r="J169" s="25"/>
@@ -8598,26 +8531,26 @@
         <v>165</v>
       </c>
       <c r="D170" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>5.8202084692851725</v>
       </c>
       <c r="E170" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F170" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>165</v>
       </c>
       <c r="G170" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>5.8202084692851725</v>
       </c>
       <c r="H170" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I170" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>5.8202084692851725</v>
       </c>
       <c r="J170" s="25"/>
@@ -8632,26 +8565,26 @@
         <v>125</v>
       </c>
       <c r="D171" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>4.4092488403675549</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F171" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G171" s="81" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H171" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I171" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4.4092488403675549</v>
       </c>
       <c r="J171" s="25"/>
@@ -8668,26 +8601,26 @@
         <v>150</v>
       </c>
       <c r="D172" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>5.2910986084410663</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F172" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>150</v>
       </c>
       <c r="G172" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>5.2910986084410663</v>
       </c>
       <c r="H172" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I172" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>5.2910986084410663</v>
       </c>
       <c r="J172" s="25"/>
@@ -8702,26 +8635,26 @@
         <v>250</v>
       </c>
       <c r="D173" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>8.8184976807351099</v>
       </c>
       <c r="E173" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F173" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G173" s="81" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H173" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I173" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>8.8184976807351099</v>
       </c>
       <c r="J173" s="25"/>
@@ -8738,26 +8671,26 @@
         <v>76</v>
       </c>
       <c r="D174" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>2.6808232949434734</v>
       </c>
       <c r="E174" s="25" t="s">
         <v>6</v>
       </c>
       <c r="F174" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>76</v>
       </c>
       <c r="G174" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>2.6808232949434734</v>
       </c>
       <c r="H174" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I174" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>2.6808232949434734</v>
       </c>
       <c r="J174" s="25"/>
@@ -8774,26 +8707,26 @@
         <v>135</v>
       </c>
       <c r="D175" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>4.7619887475969591</v>
       </c>
       <c r="E175" s="25" t="s">
         <v>18</v>
       </c>
       <c r="F175" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>135</v>
       </c>
       <c r="G175" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>4.7619887475969591</v>
       </c>
       <c r="H175" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I175" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>4.7619887475969591</v>
       </c>
       <c r="J175" s="25"/>
@@ -8810,26 +8743,26 @@
         <v>0</v>
       </c>
       <c r="D176" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F176" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G176" s="81">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="H176" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I176" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J176" s="25"/>
@@ -8845,16 +8778,16 @@
       </c>
       <c r="D177" s="21"/>
       <c r="E177" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F177" s="14"/>
       <c r="G177" s="81"/>
       <c r="H177" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I177" s="21" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="J177" s="25"/>
@@ -8869,26 +8802,26 @@
         <v>0</v>
       </c>
       <c r="D178" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F178" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G178" s="81" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H178" s="89">
-        <f t="shared" si="50"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="I178" s="21">
-        <f t="shared" si="51"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="J178" s="25"/>
@@ -8906,26 +8839,26 @@
         <v>1006</v>
       </c>
       <c r="D179" s="21">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v>35.485634667278084</v>
       </c>
       <c r="E179" s="19" t="s">
         <v>41</v>
       </c>
       <c r="F179" s="14">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v>1006</v>
       </c>
       <c r="G179" s="14">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v>35.485634667278084</v>
       </c>
       <c r="H179" s="89">
-        <f t="shared" ref="H179:H206" si="63">IF(C179="","",INT(D179/16))</f>
+        <f t="shared" ref="H179:H206" si="66">IF(C179="","",INT(D179/16))</f>
         <v>2</v>
       </c>
       <c r="I179" s="21">
-        <f t="shared" ref="I179:I206" si="64">IF(D179="","",MOD(D179,16))</f>
+        <f t="shared" ref="I179:I206" si="67">IF(D179="","",MOD(D179,16))</f>
         <v>3.4856346672780845</v>
       </c>
       <c r="J179" s="25"/>
@@ -8936,26 +8869,26 @@
       </c>
       <c r="C180" s="56"/>
       <c r="D180" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E180" s="44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F180" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G180" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H180" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I180" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J180" s="25"/>
@@ -8966,26 +8899,26 @@
       </c>
       <c r="C181" s="56"/>
       <c r="D181" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E181" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F181" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G181" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H181" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I181" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J181" s="25"/>
@@ -8996,26 +8929,26 @@
       </c>
       <c r="C182" s="56"/>
       <c r="D182" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E182" s="25" t="s">
         <v>48</v>
       </c>
       <c r="F182" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G182" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H182" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I182" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J182" s="25"/>
@@ -9026,26 +8959,26 @@
       </c>
       <c r="C183" s="56"/>
       <c r="D183" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E183" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F183" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G183" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H183" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I183" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J183" s="25"/>
@@ -9054,26 +8987,26 @@
       <c r="B184" s="18"/>
       <c r="C184" s="56"/>
       <c r="D184" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E184" s="25" t="s">
         <v>47</v>
       </c>
       <c r="F184" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G184" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H184" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I184" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J184" s="25"/>
@@ -9083,16 +9016,16 @@
       <c r="C185" s="56"/>
       <c r="D185" s="21"/>
       <c r="E185" s="42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F185" s="14"/>
       <c r="G185" s="14"/>
       <c r="H185" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I185" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J185" s="25"/>
@@ -9101,26 +9034,26 @@
       <c r="B186" s="18"/>
       <c r="C186" s="56"/>
       <c r="D186" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E186" s="42" t="s">
         <v>49</v>
       </c>
       <c r="F186" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G186" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H186" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I186" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J186" s="25"/>
@@ -9129,26 +9062,26 @@
       <c r="B187" s="18"/>
       <c r="C187" s="56"/>
       <c r="D187" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E187" s="42" t="s">
         <v>50</v>
       </c>
       <c r="F187" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G187" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H187" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I187" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J187" s="25"/>
@@ -9157,23 +9090,23 @@
       <c r="B188" s="18"/>
       <c r="C188" s="112"/>
       <c r="D188" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="F188" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G188" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H188" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I188" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J188" s="25"/>
@@ -9184,26 +9117,26 @@
       </c>
       <c r="C189" s="56"/>
       <c r="D189" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E189" s="27" t="s">
         <v>41</v>
       </c>
       <c r="F189" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G189" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H189" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I189" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J189" s="25"/>
@@ -9214,26 +9147,26 @@
       </c>
       <c r="C190" s="56"/>
       <c r="D190" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E190" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F190" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G190" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H190" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I190" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J190" s="25"/>
@@ -9244,26 +9177,26 @@
       </c>
       <c r="C191" s="56"/>
       <c r="D191" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E191" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F191" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G191" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H191" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I191" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J191" s="25"/>
@@ -9274,26 +9207,26 @@
       </c>
       <c r="C192" s="56"/>
       <c r="D192" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E192" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F192" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G192" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H192" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I192" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J192" s="25"/>
@@ -9304,26 +9237,26 @@
       </c>
       <c r="C193" s="56"/>
       <c r="D193" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E193" s="25" t="s">
         <v>4</v>
       </c>
       <c r="F193" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G193" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H193" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I193" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J193" s="25"/>
@@ -9334,26 +9267,26 @@
       </c>
       <c r="C194" s="56"/>
       <c r="D194" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E194" s="25" t="s">
         <v>5</v>
       </c>
       <c r="F194" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G194" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H194" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I194" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J194" s="25"/>
@@ -9364,26 +9297,26 @@
       </c>
       <c r="C195" s="56"/>
       <c r="D195" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E195" s="25" t="s">
         <v>46</v>
       </c>
       <c r="F195" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G195" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H195" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I195" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J195" s="25"/>
@@ -9394,26 +9327,26 @@
       </c>
       <c r="C196" s="56"/>
       <c r="D196" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E196" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F196" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G196" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H196" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I196" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J196" s="25"/>
@@ -9424,26 +9357,26 @@
       </c>
       <c r="C197" s="56"/>
       <c r="D197" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E197" s="25" t="s">
         <v>6</v>
       </c>
       <c r="F197" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G197" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H197" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I197" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J197" s="25"/>
@@ -9454,26 +9387,26 @@
       </c>
       <c r="C198" s="56"/>
       <c r="D198" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E198" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F198" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G198" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H198" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I198" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J198" s="25"/>
@@ -9484,26 +9417,26 @@
       </c>
       <c r="C199" s="56"/>
       <c r="D199" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E199" s="25" t="s">
         <v>2</v>
       </c>
       <c r="F199" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G199" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H199" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I199" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J199" s="25"/>
@@ -9514,26 +9447,26 @@
       </c>
       <c r="C200" s="56"/>
       <c r="D200" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E200" s="25" t="s">
         <v>44</v>
       </c>
       <c r="F200" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G200" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H200" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I200" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J200" s="25"/>
@@ -9544,26 +9477,26 @@
       </c>
       <c r="C201" s="56"/>
       <c r="D201" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E201" s="25" t="s">
         <v>9</v>
       </c>
       <c r="F201" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G201" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H201" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I201" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J201" s="25"/>
@@ -9574,26 +9507,26 @@
       </c>
       <c r="C202" s="56"/>
       <c r="D202" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E202" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F202" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G202" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H202" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I202" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J202" s="25"/>
@@ -9604,26 +9537,26 @@
       </c>
       <c r="C203" s="56"/>
       <c r="D203" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E203" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F203" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G203" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H203" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I203" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J203" s="25"/>
@@ -9634,26 +9567,26 @@
       </c>
       <c r="C204" s="56"/>
       <c r="D204" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E204" s="25" t="s">
         <v>11</v>
       </c>
       <c r="F204" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G204" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H204" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I204" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J204" s="25"/>
@@ -9664,26 +9597,26 @@
       </c>
       <c r="C205" s="56"/>
       <c r="D205" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E205" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F205" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G205" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H205" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I205" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J205" s="25"/>
@@ -9694,26 +9627,26 @@
       </c>
       <c r="C206" s="112"/>
       <c r="D206" s="21" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="63"/>
         <v/>
       </c>
       <c r="E206" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F206" s="14" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="64"/>
         <v/>
       </c>
       <c r="G206" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H206" s="89" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v/>
       </c>
       <c r="I206" s="21" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v/>
       </c>
       <c r="J206" s="25"/>
@@ -9727,7 +9660,7 @@
         <v/>
       </c>
       <c r="G207" s="14" t="str">
-        <f t="shared" si="62"/>
+        <f t="shared" si="65"/>
         <v/>
       </c>
       <c r="H207" s="90"/>
@@ -9736,7 +9669,7 @@
     </row>
     <row r="208" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="124" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C208" s="56"/>
       <c r="D208" s="21"/>
@@ -9758,10 +9691,10 @@
         <v>752.11203019453603</v>
       </c>
       <c r="E209" s="65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F209" s="63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G209" s="64" t="s">
         <v>1</v>
@@ -9956,25 +9889,25 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND(COUNTBLANK($C$3)=0,$C$3=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B206">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>AND($B3="x",AND(COUNTBLANK($C3)=0,$C3=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C206">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>AND(COUNTBLANK($C3)=0,$C3=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E216">
-    <cfRule type="containsText" dxfId="6" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
+    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
       <formula>NOT(ISERROR(SEARCH("~*~*",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="~*">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="~*">
       <formula>NOT(ISERROR(SEARCH("~*",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10039,25 +9972,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" t="str">
         <v>Blue Pack</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2" t="str">
         <v>pot .7 gt cup &amp; windscreen</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F2" t="str">
         <v>Maps</v>
       </c>
       <c r="G2" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H2" t="str">
         <v>Medication</v>
@@ -10065,25 +9998,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" t="str">
         <v>Pack hip pockets</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D3" t="str">
         <v>IsoPro Stove w/ ignitor</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F3" t="str">
         <v>Compass</v>
       </c>
       <c r="G3" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H3" t="str">
         <v>24-32 ounces food per day</v>
@@ -10091,25 +10024,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B4" t="str">
         <v>Pack Liner/Garbage bag</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D4" t="str">
         <v>IsoPro canister 8oz</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F4" t="str">
         <v>Trail details</v>
       </c>
       <c r="G4" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H4" t="str">
         <v>64 ounces water</v>
@@ -10117,19 +10050,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" t="str">
         <v>Orange Pack Cover</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D5" t="str">
         <v>IsoPro canister stand</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F5" t="str">
         <v>pen / pencil</v>
@@ -10143,13 +10076,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" t="str">
         <v>cozy for freezer bag meals</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F6" t="str">
         <v>notepad / journal</v>
@@ -10164,7 +10097,7 @@
         <v>Shelter Group</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" t="str">
         <v>lighter</v>
@@ -10174,7 +10107,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H7" t="str">
         <v>trekking poles</v>
@@ -10182,13 +10115,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" t="str">
         <v>Bridge Hammock; 1.2 Hexon Olive</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D8" t="str">
         <v>spork short</v>
@@ -10198,7 +10131,7 @@
         <v>First Aid Group</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H8" t="str">
         <v>hiking boots</v>
@@ -10206,25 +10139,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B9" t="str">
         <v>Spreader Bars 28"</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" t="str">
         <v>spoon long</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F9" t="str">
         <v>First aid kit</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H9" t="str">
         <v>liner socks</v>
@@ -10232,13 +10165,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B10" t="str">
         <v>Tree straps spider poly</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" t="str">
         <v>3 liter bladder</v>
@@ -10248,7 +10181,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G10" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H10" t="str">
         <v>wool socks</v>
@@ -10256,13 +10189,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B11" t="str">
         <v>UCR</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="str">
         <v>water bottles collapsable</v>
@@ -10272,7 +10205,7 @@
         <v>Repair Group</v>
       </c>
       <c r="G11" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H11" t="str">
         <v>gators</v>
@@ -10280,25 +10213,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" t="str">
         <v>Tarp Forest green &amp; lines</v>
       </c>
       <c r="C12" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="str">
         <v>smart water bottles</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F12" t="str">
         <v>Tenacious tape</v>
       </c>
       <c r="G12" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H12" t="str">
         <v>tech shirt</v>
@@ -10306,25 +10239,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" t="str">
         <v>stakes AL red</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D13" t="str">
         <v>Water Filter Kit</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F13" t="str">
         <v>Duct tape on trekking poles</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H13" t="str">
         <v>underwear</v>
@@ -10332,25 +10265,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B14" t="str">
         <v>Tyvek 4x3</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D14" t="str">
         <v xml:space="preserve">  --Filter  (New: Versa Filter)</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F14" t="str">
         <v>extra buckle</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H14" t="str">
         <v>Kilt / Zip-offs</v>
@@ -10358,13 +10291,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" t="str">
         <v>Mylar blanket</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D15" t="str">
         <v xml:space="preserve">   --CNOC 3 liter</v>
@@ -10374,7 +10307,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H15" t="str">
         <v>runners cap</v>
@@ -10385,7 +10318,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D16" t="str">
         <v xml:space="preserve">  --tubing</v>
@@ -10395,7 +10328,7 @@
         <v>Misc Group</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H16" t="str">
         <v>pocket knife</v>
@@ -10406,19 +10339,19 @@
         <v>Sleeping Group</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D17" t="str">
         <v xml:space="preserve">  --sawyer squeze</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F17" t="str">
         <v>phone battery 4,000mAh</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H17" t="str">
         <v>lip balm</v>
@@ -10426,25 +10359,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B18" t="str">
         <v>15° sleeping bag - Katahdin</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D18" t="str">
         <v xml:space="preserve">  --bleach/polar pure/ tablets</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F18" t="str">
         <v>Camp chair - heavy</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H18" t="str">
         <v>phone (in zip-loc)</v>
@@ -10452,25 +10385,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" t="str">
         <v>sleeping bag liner blue</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D19" t="str">
         <v>food bag Blue</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F19" t="str">
         <v>hammock chair (green)</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H19" t="str">
         <v>license / money / credit card</v>
@@ -10478,25 +10411,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B20" t="str">
         <v>pillow black (Outdoor Vitals)</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D20" t="str">
         <v>bear bag and rope</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F20" t="str">
         <v>head lamp</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H20" t="str">
         <v>bandana</v>
@@ -10504,25 +10437,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B21" t="str">
-        <v>Under Quilt</v>
+        <v>Under Quilt Blue 5.0 Climashield</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" t="str">
         <v>red bandana</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F21" t="str">
         <v>spare batteries 3 AAA</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H21" t="str">
         <v>belt</v>
@@ -10530,7 +10463,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B22" t="str">
         <v xml:space="preserve"> </v>
@@ -10540,13 +10473,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F22" t="str">
         <v>rope pieces</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H22" t="str">
         <v>suspenders</v>
@@ -10562,7 +10495,7 @@
         <v>Hygiene Group</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F23" t="str">
         <v>eye glass case - soft</v>
@@ -10574,13 +10507,13 @@
         <v>Down booties</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D24" t="str">
         <v>Bathroom kit</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F24" t="str">
         <v>foam pad 12 x 18</v>
@@ -10588,13 +10521,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B25" t="str">
         <v>Fleece hat</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" t="str">
         <v xml:space="preserve">  --TP</v>
@@ -10606,13 +10539,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B26" t="str">
         <v>long sleeve shirt</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" t="str">
         <v xml:space="preserve">  --wet wipes</v>
@@ -10624,19 +10557,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B27" t="str">
         <v>underwear</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D27" t="str">
         <v xml:space="preserve">  -- hand sanitizer</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F27" t="str">
         <v>puffy</v>
@@ -10644,19 +10577,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" t="str">
         <v>Wool socks</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D28" t="str">
         <v xml:space="preserve">  --Gold Bond</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F28" t="str">
         <v>gloves/mittens</v>
@@ -10664,19 +10597,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B29" t="str">
         <v>Liner socks</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D29" t="str">
         <v>Shovel plastic</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F29" t="str">
         <v>Liner socks</v>
@@ -10684,19 +10617,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" t="str">
         <v>running tights *</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D30" t="str">
         <v>water jug botom</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" t="str">
         <v>Wool socks</v>
@@ -10704,19 +10637,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" t="str">
         <v>camp shoes</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D31" t="str">
         <v>tooth brush</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F31" t="str">
         <v xml:space="preserve">long sleeve shirt </v>
@@ -10724,19 +10657,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B32" t="str">
         <v xml:space="preserve"> </v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D32" t="str">
         <v>tooth  dots / paste</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F32" t="str">
         <v>underwear</v>
@@ -10747,13 +10680,13 @@
         <v>Rain Gear Group</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D33" t="str">
         <v>hand sanitizer on pack</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F33" t="str">
         <v>shorts</v>
@@ -10768,7 +10701,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F34" t="str">
         <v>zip-offs</v>
@@ -10776,7 +10709,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B35" t="str">
         <v>Rain pants blue FroggTog</v>
@@ -10788,21 +10721,21 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B36" t="str">
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B16:H18 A18 B32:H33 A1:H15 A32 A34:H44 A19:H31">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="Pounds">
+  <conditionalFormatting sqref="A1:H15 B16:H18 A18 A19:H31 A32 B32:H33 A34:H44">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Pounds">
       <formula>NOT(ISERROR(SEARCH("Pounds",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="Ounces">
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="Ounces">
       <formula>NOT(ISERROR(SEARCH("Ounces",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11157,7 +11090,7 @@
         <v>31.676043669200517</v>
       </c>
       <c r="C21" t="str">
-        <v>Under Quilt</v>
+        <v>Under Quilt Blue 5.0 Climashield</v>
       </c>
       <c r="D21" s="109">
         <v>1</v>
@@ -11698,7 +11631,7 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="101">
-        <v>0</v>
+        <v>1.4462336196405581</v>
       </c>
       <c r="C55" t="str">
         <v>food bag Blue</v>
@@ -11706,8 +11639,8 @@
       <c r="D55" s="109">
         <v>0</v>
       </c>
-      <c r="E55" s="106" t="str">
-        <v/>
+      <c r="E55" s="106">
+        <v>1.4462336196405581</v>
       </c>
       <c r="I55" s="86"/>
       <c r="J55" s="84"/>
@@ -12815,10 +12748,10 @@
     <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="102">
         <f>SUM(B1:B127)</f>
-        <v>756.80347096068772</v>
+        <v>758.24970458032828</v>
       </c>
       <c r="C131" s="69" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D131" s="110"/>
       <c r="E131" s="107"/>
@@ -12834,7 +12767,7 @@
         <v>47</v>
       </c>
       <c r="C132" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D132" s="110"/>
       <c r="E132" s="107"/>
@@ -12846,10 +12779,10 @@
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="104">
         <f>MOD(B131,16)</f>
-        <v>4.8034709606877186</v>
+        <v>6.2497045803282845</v>
       </c>
       <c r="C133" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D133" s="110"/>
       <c r="E133" s="107"/>
@@ -12858,7 +12791,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:G124 C131:G151">
-    <cfRule type="containsText" dxfId="14" priority="13" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12890,10 +12823,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>1</v>
@@ -12944,7 +12877,7 @@
         <v>1296</v>
       </c>
       <c r="H3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -12994,10 +12927,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C8" s="86" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -13009,16 +12942,16 @@
         <v>1</v>
       </c>
       <c r="H8" s="85" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I8" s="113" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J8" s="113" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="123" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -13043,7 +12976,7 @@
         <v>25.53836928340888</v>
       </c>
       <c r="H9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I9">
         <f>INT(G9/16)</f>
@@ -13062,7 +12995,7 @@
         <v>10.666666666666668</v>
       </c>
       <c r="N9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -13079,7 +13012,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F10">
         <v>193</v>
@@ -13089,7 +13022,7 @@
         <v>6.8078802095275055</v>
       </c>
       <c r="H10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I10">
         <f>INT(G10/16)</f>
@@ -13107,7 +13040,7 @@
         <v>4.0200000000000005</v>
       </c>
       <c r="N10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13131,7 +13064,7 @@
         <v>10.688019189050953</v>
       </c>
       <c r="H11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I11">
         <f>INT(G11/16)</f>
@@ -13167,7 +13100,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="H12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I12">
         <f>INT(G12/16)</f>
@@ -13192,7 +13125,7 @@
         <v>10.970211114834477</v>
       </c>
       <c r="E13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F13">
         <v>37</v>
@@ -13202,7 +13135,7 @@
         <v>1.3051376567487962</v>
       </c>
       <c r="H13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I13">
         <f>INT(G13/16)</f>
@@ -13252,10 +13185,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>1</v>
@@ -13285,7 +13218,7 @@
         <v>17.284255454240817</v>
       </c>
       <c r="H18" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I18">
         <f>INT(G18/16)</f>
@@ -13338,7 +13271,7 @@
         <v>61.976401700206353</v>
       </c>
       <c r="H21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I21">
         <f>INT(G21/16)</f>
@@ -13351,10 +13284,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C22" s="86" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>1</v>
@@ -13460,12 +13393,12 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
@@ -13474,16 +13407,16 @@
         <v>1</v>
       </c>
       <c r="I30" s="113" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J30" s="113" t="s">
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O30" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -13502,7 +13435,7 @@
       </c>
       <c r="J31" s="9"/>
       <c r="L31" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M31">
         <v>0.9</v>
@@ -13539,14 +13472,14 @@
         <v>28.166666666666664</v>
       </c>
       <c r="H32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I32">
-        <f t="shared" ref="I32:I35" si="0">INT(G32/16)</f>
+        <f t="shared" ref="I32:I33" si="0">INT(G32/16)</f>
         <v>1</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" ref="J32:J35" si="1">MOD(G32,16)</f>
+        <f t="shared" ref="J32:J33" si="1">MOD(G32,16)</f>
         <v>12.166666666666664</v>
       </c>
       <c r="L32" s="9">
@@ -13588,11 +13521,11 @@
         <v>737.08699999999999</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33:J34" si="2">F33/$G$1</f>
+        <f t="shared" ref="G33:G34" si="2">F33/$G$1</f>
         <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -13645,7 +13578,7 @@
         <v>54.166666666666664</v>
       </c>
       <c r="H34" s="116" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I34" s="116">
         <f>SUM(I32:I33)</f>
@@ -13677,7 +13610,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="H35" s="117" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I35" s="117">
         <f>INT(G35/16)</f>
@@ -13688,7 +13621,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="K35" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -13710,7 +13643,7 @@
         <v>1.6931515547011413</v>
       </c>
       <c r="H36" s="120" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I36" s="120">
         <f>INT(G36/16)</f>
@@ -13754,7 +13687,7 @@
         <v>22.313333333333325</v>
       </c>
       <c r="H38" s="122" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I38" s="122">
         <f t="shared" ref="I38" si="3">INT(G38/16)</f>
@@ -13765,7 +13698,7 @@
         <v>6.3133333333333255</v>
       </c>
       <c r="L38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -13785,7 +13718,7 @@
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -13805,7 +13738,7 @@
         <v>3.6</v>
       </c>
       <c r="M40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -13825,7 +13758,7 @@
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -13833,7 +13766,7 @@
         <v>31.676043669200517</v>
       </c>
       <c r="B42" s="116" t="str">
-        <v>Under Quilt</v>
+        <v>Under Quilt Blue 5.0 Climashield</v>
       </c>
       <c r="C42" s="116">
         <v>1</v>
@@ -13845,7 +13778,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -13865,7 +13798,7 @@
         <v>7.5</v>
       </c>
       <c r="M43" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -13874,7 +13807,7 @@
         <v>76.47999999999999</v>
       </c>
       <c r="B45" s="116" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C45" s="116">
         <f t="shared" ref="C45" si="5">INT(A45/16)</f>

--- a/AT/GearListNew.xlsx
+++ b/AT/GearListNew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1108" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{333B2FE3-6D6B-4859-95EB-739BE215FF09}"/>
+  <xr:revisionPtr revIDLastSave="1194" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4013FAE-664E-4B0F-83A0-0555F1E70A6D}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="1005" windowWidth="27210" windowHeight="15195" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
+    <workbookView xWindow="360" yWindow="840" windowWidth="27435" windowHeight="14730" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gear Checklist" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="272">
   <si>
     <t>gm</t>
   </si>
@@ -288,9 +288,6 @@
   </si>
   <si>
     <t>tent inside</t>
-  </si>
-  <si>
-    <t>Air matress Big Birtha</t>
   </si>
   <si>
     <t>Air matress blue</t>
@@ -861,15 +858,9 @@
     <t>straps, stakes, shock cord, bag</t>
   </si>
   <si>
-    <t>Griz Arieal Hammock; 1.6ox Hexon</t>
-  </si>
-  <si>
     <t>New Pack Cover x</t>
   </si>
   <si>
-    <t>15° sleeping bag - Katahdin</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -940,6 +931,36 @@
   </si>
   <si>
     <t>get dimensions</t>
+  </si>
+  <si>
+    <t>Griz Arieal Hammock; 1.2ox Hexon; Dak Olive</t>
+  </si>
+  <si>
+    <t>30° sleeping bag</t>
+  </si>
+  <si>
+    <t>Backpacks</t>
+  </si>
+  <si>
+    <t>Packcover</t>
+  </si>
+  <si>
+    <t>Hammocks</t>
+  </si>
+  <si>
+    <t>AirMatresses</t>
+  </si>
+  <si>
+    <t>SleepingBags</t>
+  </si>
+  <si>
+    <t>SleepingBagLiners</t>
+  </si>
+  <si>
+    <t>Tarps</t>
+  </si>
+  <si>
+    <t>Selection Name</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1633,12 +1654,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{11F929FC-84B5-425F-A422-9C245DCEA07D}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1719,10 +1758,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2029,17 +2064,18 @@
     <col min="2" max="2" width="3.42578125" style="15" customWidth="1"/>
     <col min="3" max="3" width="6" style="59" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="41.7109375" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="19" customWidth="1"/>
     <col min="7" max="7" width="6.5703125" style="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.42578125" style="87" customWidth="1"/>
     <col min="9" max="9" width="5.85546875" style="19" customWidth="1"/>
-    <col min="10" max="10" width="32.140625" style="19" customWidth="1"/>
+    <col min="10" max="10" width="41.5703125" style="19" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4" style="19" customWidth="1"/>
     <col min="12" max="12" width="2.140625" style="19" customWidth="1"/>
     <col min="13" max="13" width="10.140625" style="36" customWidth="1"/>
-    <col min="14" max="14" width="31.85546875" style="19" customWidth="1"/>
-    <col min="15" max="16" width="8.7109375" style="19" customWidth="1"/>
+    <col min="14" max="14" width="33" style="19" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" style="19" customWidth="1"/>
     <col min="17" max="17" width="13.28515625" style="19" customWidth="1"/>
     <col min="18" max="19" width="8.7109375" style="19" customWidth="1"/>
     <col min="20" max="20" width="19" style="19" customWidth="1"/>
@@ -2057,10 +2093,10 @@
         <v>17</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
@@ -2083,16 +2119,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L2" s="26"/>
       <c r="M2" s="35"/>
@@ -2122,24 +2158,26 @@
         <v>0</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="72" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K3" s="26"/>
       <c r="L3" s="26"/>
       <c r="M3" s="35"/>
       <c r="N3" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="O3" s="26"/>
+        <v>158</v>
+      </c>
+      <c r="O3" s="40" t="s">
+        <v>271</v>
+      </c>
       <c r="P3" s="26"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="26"/>
@@ -2148,7 +2186,7 @@
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>42</v>
@@ -2185,14 +2223,16 @@
       </c>
       <c r="K4" s="20"/>
       <c r="L4" s="20"/>
-      <c r="M4" s="21">
-        <f>VLOOKUP(N4,E4:G8,3,FALSE)</f>
-        <v>45.50344803259317</v>
-      </c>
-      <c r="N4" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="O4" s="20"/>
+      <c r="M4" s="21" cm="1">
+        <f t="array" ref="M4">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N4=$E$1:$E$207)</f>
+        <v>41.446939099455015</v>
+      </c>
+      <c r="N4" s="125" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>264</v>
+      </c>
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
       <c r="R4" s="20"/>
@@ -2232,14 +2272,16 @@
       </c>
       <c r="K5" s="20"/>
       <c r="L5" s="20"/>
-      <c r="M5" s="21">
-        <f>VLOOKUP(N5,E11:G13,3,FALSE)</f>
+      <c r="M5" s="21" cm="1">
+        <f t="array" ref="M5">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N5=$E$1:$E$207)</f>
         <v>5.1500026455493044</v>
       </c>
       <c r="N5" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="25"/>
+      <c r="O5" s="25" t="s">
+        <v>265</v>
+      </c>
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25"/>
@@ -2274,20 +2316,22 @@
         <v>0</v>
       </c>
       <c r="J6" s="74" t="str">
-        <v>Griz Arieal Hammock; 1.6ox Hexon</v>
+        <v>Griz Arieal Hammock; 1.2ox Hexon; Dak Olive</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>42</v>
       </c>
       <c r="L6" s="20"/>
-      <c r="M6" s="21">
-        <f>VLOOKUP(N6,E16:G19,3,FALSE)</f>
+      <c r="M6" s="21" cm="1">
+        <f t="array" ref="M6">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N6=$E$1:$E$207)</f>
         <v>8.2188398384451222</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="O6" s="25"/>
+        <v>200</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>266</v>
+      </c>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
       <c r="R6" s="25"/>
@@ -2326,14 +2370,16 @@
       </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
-      <c r="M7" s="21" t="str">
-        <f>VLOOKUP(N7,E50:G51,3,FALSE)</f>
-        <v/>
+      <c r="M7" s="21" cm="1">
+        <f t="array" ref="M7">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N7=$E$1:$E$207)</f>
+        <v>17.213707472794937</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="O7" s="25"/>
+        <v>72</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>267</v>
+      </c>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
       <c r="R7" s="25"/>
@@ -2372,14 +2418,16 @@
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
-      <c r="M8" s="21">
-        <f>VLOOKUP(N8,E42:G45,3,FALSE)</f>
-        <v>44.797968218134358</v>
+      <c r="M8" s="21" cm="1">
+        <f t="array" ref="M8">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N8=$E$1:$E$207)</f>
+        <v>38.378101906559202</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="O8" s="25"/>
+        <v>263</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>268</v>
+      </c>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
       <c r="R8" s="25"/>
@@ -2388,7 +2436,7 @@
     </row>
     <row r="9" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>42</v>
@@ -2424,14 +2472,16 @@
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
-      <c r="M9" s="21" t="str">
-        <f>VLOOKUP(N9,E46:G47,3,FALSE)</f>
-        <v/>
+      <c r="M9" s="21" cm="1">
+        <f t="array" ref="M9">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N9=$E$1:$E$207)</f>
+        <v>0</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="O9" s="25"/>
+        <v>100</v>
+      </c>
+      <c r="O9" s="25" t="s">
+        <v>269</v>
+      </c>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
       <c r="R9" s="25"/>
@@ -2440,7 +2490,7 @@
     </row>
     <row r="10" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>42</v>
@@ -2476,9 +2526,16 @@
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
+      <c r="M10" s="21" cm="1">
+        <f t="array" ref="M10">_xlfn._xlws.FILTER(_xlfn.CHOOSECOLS($D$1:$I$207,1),N10=$E$1:$E$207)</f>
+        <v>16.71987160267377</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="O10" s="25" t="s">
+        <v>270</v>
+      </c>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
       <c r="R10" s="25"/>
@@ -2529,7 +2586,7 @@
     </row>
     <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>42</v>
@@ -2582,7 +2639,7 @@
         <v/>
       </c>
       <c r="E13" s="31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F13" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2709,7 +2766,7 @@
         <v>13.545212437609129</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F16" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2741,7 +2798,7 @@
     </row>
     <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>42</v>
@@ -2754,7 +2811,7 @@
         <v>8.2188398384451222</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F17" s="20">
         <f t="shared" si="1"/>
@@ -2792,7 +2849,7 @@
         <v/>
       </c>
       <c r="E18" s="114" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="F18" s="20" t="str">
         <f t="shared" ref="F18:F19" si="6">IF(B18="x",IF(C18=0,"",C18),"")</f>
@@ -2862,7 +2919,7 @@
     </row>
     <row r="20" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>42</v>
@@ -2875,7 +2932,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F20" s="20">
         <f t="shared" ref="F20:F21" si="10">IF(B20="x",IF(C20=0,"",C20),"")</f>
@@ -2914,7 +2971,7 @@
         <v>7.9719219033845397</v>
       </c>
       <c r="E21" s="80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F21" s="20" t="str">
         <f t="shared" si="10"/>
@@ -2986,7 +3043,7 @@
     </row>
     <row r="23" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>42</v>
@@ -2999,7 +3056,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F23" s="20">
         <f t="shared" si="1"/>
@@ -3018,7 +3075,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -3073,7 +3130,7 @@
     </row>
     <row r="25" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>42</v>
@@ -3086,7 +3143,7 @@
         <v>1.4109596289176176</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F25" s="20">
         <f t="shared" si="1"/>
@@ -3158,7 +3215,7 @@
     </row>
     <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>42</v>
@@ -3171,7 +3228,7 @@
         <v>16.71987160267377</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" s="20">
         <v>300</v>
@@ -3189,7 +3246,7 @@
         <v>0.71987160267376993</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
@@ -3204,7 +3261,7 @@
     </row>
     <row r="28" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>42</v>
@@ -3289,7 +3346,7 @@
     </row>
     <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C30" s="56">
         <v>126</v>
@@ -3331,7 +3388,7 @@
     </row>
     <row r="31" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C31" s="56">
         <v>311</v>
@@ -3373,7 +3430,7 @@
     </row>
     <row r="32" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C32" s="56">
         <v>0</v>
@@ -3402,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>42</v>
@@ -3419,7 +3476,7 @@
     </row>
     <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C33" s="56">
         <v>545</v>
@@ -3461,7 +3518,7 @@
     </row>
     <row r="34" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C34" s="56">
         <v>305</v>
@@ -3513,7 +3570,7 @@
         <v>2.5044533413287713</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" s="20">
         <f t="shared" si="1"/>
@@ -3545,7 +3602,7 @@
     </row>
     <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="56">
@@ -3556,7 +3613,7 @@
         <v>4.1976048960299126</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F36" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3596,7 +3653,7 @@
         <v>6.878428190973386</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F37" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3635,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F38" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3677,7 +3734,7 @@
         <v>1.3756856381946772</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F39" s="20">
         <f t="shared" si="1"/>
@@ -3757,7 +3814,7 @@
         <v/>
       </c>
       <c r="E41" s="44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F41" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3799,7 +3856,7 @@
         <v>38.378101906559202</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F42" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3841,7 +3898,7 @@
         <v>44.797968218134358</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F43" s="20">
         <f t="shared" si="1"/>
@@ -3881,7 +3938,7 @@
         <v>55.203795481401791</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F44" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3921,7 +3978,7 @@
         <v>38.413375897282137</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F45" s="20" t="str">
         <f t="shared" ref="F45" si="12">IF(B45="x",IF(C45=0,"",C45),"")</f>
@@ -3963,7 +4020,7 @@
         <v>6.2082223672375179</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F46" s="20">
         <f t="shared" si="1"/>
@@ -4002,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F47" s="20" t="str">
         <f t="shared" ref="F47" si="14">IF(B47="x",IF(C47=0,"",C47),"")</f>
@@ -4021,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K47" s="14" t="s">
         <v>42</v>
@@ -4046,7 +4103,7 @@
         <v>3.033563202172878</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F48" s="20" t="str">
         <f t="shared" ref="F48" si="17">IF(B48="x",IF(C48=0,"",C48),"")</f>
@@ -4088,7 +4145,7 @@
         <v>3.1746591650646399</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="20">
         <f t="shared" ref="F49" si="19">IF(B49="x",IF(C49=0,"",C49),"")</f>
@@ -4127,7 +4184,7 @@
         <v>25.079807404010655</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F50" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4159,7 +4216,7 @@
     </row>
     <row r="51" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="56">
@@ -4170,7 +4227,7 @@
         <v>17.213707472794937</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F51" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4206,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F52" s="20" t="str">
         <f t="shared" ref="F52" si="21">IF(B52="x",IF(C52=0,"",C52),"")</f>
@@ -4250,7 +4307,7 @@
         <v>31.676043669200517</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F53" s="20">
         <f t="shared" si="1"/>
@@ -4269,7 +4326,7 @@
         <v>15.676043669200517</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K53" s="20"/>
       <c r="L53" s="20"/>
@@ -4286,7 +4343,7 @@
       <c r="C54" s="56"/>
       <c r="D54" s="21"/>
       <c r="E54" s="25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="21"/>
@@ -4359,7 +4416,7 @@
         <v/>
       </c>
       <c r="E56" s="27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F56" s="20" t="str">
         <f t="shared" si="23"/>
@@ -4401,7 +4458,7 @@
         <v>2.9630152207269971</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="20">
         <f t="shared" si="23"/>
@@ -4443,7 +4500,7 @@
         <v>3.280481137233461</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F58" s="20">
         <f t="shared" si="1"/>
@@ -4482,7 +4539,7 @@
         <v>1.0934937124111537</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F59" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4521,7 +4578,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F60" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4563,7 +4620,7 @@
         <v>5.2205506269951849</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F61" s="20">
         <f t="shared" si="1"/>
@@ -4686,7 +4743,7 @@
         <v>5.8554824600081128</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="1"/>
@@ -4728,7 +4785,7 @@
         <v>1.6578775639782006</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" ref="F65" si="25">IF(B65="x",IF(C65=0,"",C65),"")</f>
@@ -4890,7 +4947,7 @@
         <v>13.580486428332069</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="27"/>
@@ -4973,7 +5030,7 @@
         <v/>
       </c>
       <c r="E71" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F71" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5015,7 +5072,7 @@
         <v>8.6068537363974684</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F72" s="14">
         <f t="shared" si="27"/>
@@ -5055,7 +5112,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F73" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5074,7 +5131,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K73" s="20"/>
       <c r="L73" s="20"/>
@@ -5097,7 +5154,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="E74" s="45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F74" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5116,7 +5173,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -5139,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F75" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5181,7 +5238,7 @@
         <v>4.5503448032593168</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F76" s="14">
         <f t="shared" ref="F76" si="33">IF(B76="x",IF(C76=0,"",C76),"")</f>
@@ -5220,7 +5277,7 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="E77" s="46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F77" s="14" t="str">
         <f t="shared" ref="F77" si="35">IF(B77="x",IF(C77=0,"",C77),"")</f>
@@ -5239,7 +5296,7 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K77" s="20" t="s">
         <v>42</v>
@@ -5347,7 +5404,7 @@
         <v/>
       </c>
       <c r="E80" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F80" s="14" t="str">
         <f t="shared" ref="F80:F151" si="37">IF(B80="x",IF(C80=0,"",C80),"")</f>
@@ -5366,7 +5423,7 @@
         <v/>
       </c>
       <c r="J80" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K80" s="20"/>
       <c r="L80" s="20"/>
@@ -5388,7 +5445,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F81" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5430,7 +5487,7 @@
         <v>2.7513712763893543</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F82" s="14">
         <f t="shared" si="37"/>
@@ -5472,7 +5529,7 @@
         <v>3.8801389795234487</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F83" s="14">
         <f t="shared" si="37"/>
@@ -5512,7 +5569,7 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="E84" s="46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F84" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5531,7 +5588,7 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="J84" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K84" s="20" t="s">
         <v>42</v>
@@ -5556,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F85" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5598,7 +5655,7 @@
         <v>8.0071958941074808</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F86" s="14">
         <f t="shared" si="37"/>
@@ -5638,7 +5695,7 @@
         <v>4.0212349424152105</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F87" s="14" t="str">
         <f t="shared" ref="F87" si="40">IF(B87="x",IF(C87=0,"",C87),"")</f>
@@ -5678,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F88" s="14" t="str">
         <f t="shared" ref="F88:F97" si="42">IF(B88="x",IF(C88=0,"",C88),"")</f>
@@ -5720,7 +5777,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F89" s="14">
         <f t="shared" si="42"/>
@@ -5762,7 +5819,7 @@
         <v>0.91712375879645147</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F90" s="14">
         <f t="shared" si="42"/>
@@ -5804,7 +5861,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F91" s="14">
         <f t="shared" si="42"/>
@@ -5844,7 +5901,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F92" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5884,7 +5941,7 @@
         <v>0.4938358701211662</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F93" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5926,7 +5983,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F94" s="14">
         <f t="shared" si="42"/>
@@ -5968,7 +6025,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F95" s="14">
         <f t="shared" si="42"/>
@@ -6010,7 +6067,7 @@
         <v>7.372264061094552</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F96" s="14">
         <f t="shared" si="42"/>
@@ -6052,7 +6109,7 @@
         <v>1.2345896753029155</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F97" s="14">
         <f t="shared" si="42"/>
@@ -6094,7 +6151,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F98" s="14">
         <f t="shared" ref="F98" si="44">IF(B98="x",IF(C98=0,"",C98),"")</f>
@@ -6176,7 +6233,7 @@
         <v/>
       </c>
       <c r="E100" s="48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F100" s="14"/>
       <c r="G100" s="81"/>
@@ -6189,7 +6246,7 @@
         <v/>
       </c>
       <c r="J100" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -6212,7 +6269,7 @@
         <v/>
       </c>
       <c r="E101" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F101" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6252,7 +6309,7 @@
         <v/>
       </c>
       <c r="E102" s="48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F102" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6292,7 +6349,7 @@
         <v/>
       </c>
       <c r="E103" s="48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F103" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6332,7 +6389,7 @@
         <v/>
       </c>
       <c r="E104" s="48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F104" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6372,7 +6429,7 @@
         <v>1.6226035732552604</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F105" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6414,7 +6471,7 @@
         <v>1.4462336196405581</v>
       </c>
       <c r="E106" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F106" s="14">
         <f t="shared" si="37"/>
@@ -6616,7 +6673,7 @@
         <v/>
       </c>
       <c r="E111" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F111" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6698,7 +6755,7 @@
         <v/>
       </c>
       <c r="E113" s="53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F113" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6738,7 +6795,7 @@
         <v/>
       </c>
       <c r="E114" s="53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F114" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6773,7 +6830,7 @@
         <v/>
       </c>
       <c r="E115" s="54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F115" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6807,7 +6864,7 @@
         <v/>
       </c>
       <c r="E116" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F116" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6841,7 +6898,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F117" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6877,7 +6934,7 @@
         <v>1.8342475175929029</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F118" s="14">
         <f t="shared" si="37"/>
@@ -6909,7 +6966,7 @@
         <v>0.74075380518174927</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F119" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6941,7 +6998,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F120" s="14">
         <f t="shared" si="37"/>
@@ -7005,7 +7062,7 @@
         <v>0.77602779590468973</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F122" s="14">
         <f t="shared" si="37"/>
@@ -7035,7 +7092,7 @@
         <v>2.1517134340993671</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F123" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7067,7 +7124,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F124" s="14">
         <f t="shared" si="37"/>
@@ -7130,7 +7187,7 @@
         <v/>
       </c>
       <c r="E126" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F126" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7192,7 +7249,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F128" s="14">
         <f t="shared" si="37"/>
@@ -7349,7 +7406,7 @@
         <v/>
       </c>
       <c r="E133" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F133" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7381,7 +7438,7 @@
         <v>5.6438385156704705</v>
       </c>
       <c r="E134" s="66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F134" s="14">
         <f t="shared" si="37"/>
@@ -7409,7 +7466,7 @@
         <v/>
       </c>
       <c r="E135" s="66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F135" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7437,7 +7494,7 @@
         <v/>
       </c>
       <c r="E136" s="66" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F136" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7497,7 +7554,7 @@
         <v/>
       </c>
       <c r="E138" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F138" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7529,7 +7586,7 @@
         <v>0.42328788867528527</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F139" s="14">
         <f t="shared" si="37"/>
@@ -7559,7 +7616,7 @@
         <v/>
       </c>
       <c r="E140" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F140" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7591,7 +7648,7 @@
         <v>1.3404116474717367</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F141" s="14">
         <f t="shared" si="37"/>
@@ -7654,7 +7711,7 @@
         <v/>
       </c>
       <c r="E143" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F143" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7688,7 +7745,7 @@
         <v>6.5256882837439818</v>
       </c>
       <c r="E144" s="58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F144" s="58" t="str">
         <f t="shared" si="37"/>
@@ -7720,7 +7777,7 @@
         <v>4.7619887475969591</v>
       </c>
       <c r="E145" s="58" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F145" s="58">
         <f t="shared" ref="F145" si="56">IF(B145="x",IF(C145=0,"",C145),"")</f>
@@ -7799,7 +7856,7 @@
         <v>1.9897352686996257</v>
       </c>
       <c r="J147" s="67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K147" s="19" t="s">
         <v>42</v>
@@ -7817,7 +7874,7 @@
         <v>35.273990722940439</v>
       </c>
       <c r="E148" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F148" s="14">
         <f t="shared" si="37"/>
@@ -7849,7 +7906,7 @@
         <v>4.6208927847051982</v>
       </c>
       <c r="E149" s="50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F149" s="14">
         <f t="shared" si="37"/>
@@ -7912,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F151" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7944,7 +8001,7 @@
         <v>1.269863666025856</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F152" s="14">
         <f t="shared" ref="F152:F162" si="58">IF(B152="x",IF(C152=0,"",C152),"")</f>
@@ -7976,7 +8033,7 @@
         <v>2.539727332051712</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F153" s="14" t="str">
         <f t="shared" ref="F153" si="61">IF(B153="x",IF(C153=0,"",C153),"")</f>
@@ -8007,7 +8064,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F154" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8070,7 +8127,7 @@
         <v>0.70547981445880881</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F156" s="14">
         <f t="shared" si="58"/>
@@ -8101,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F157" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8193,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F160" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8226,7 +8283,7 @@
         <v>1.7284255454240816</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F161" s="14">
         <f t="shared" si="58"/>
@@ -8256,7 +8313,7 @@
         <v>3.3157551279564013</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F162" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8286,7 +8343,7 @@
         <v>3.1041111836187589</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F163" s="14" t="str">
         <f t="shared" ref="F163:F206" si="64">IF(B163="x",IF(C163=0,"",C163),"")</f>
@@ -8357,7 +8414,7 @@
         <v/>
       </c>
       <c r="E165" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F165" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8429,7 +8486,7 @@
         <v>3.8095909980775677</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F167" s="14">
         <f t="shared" si="64"/>
@@ -8463,7 +8520,7 @@
         <v>1.269863666025856</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F168" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8499,7 +8556,7 @@
         <v>1.763699536147022</v>
       </c>
       <c r="E169" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F169" s="14">
         <f t="shared" si="64"/>
@@ -8535,7 +8592,7 @@
         <v>5.8202084692851725</v>
       </c>
       <c r="E170" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F170" s="14">
         <f t="shared" si="64"/>
@@ -8569,7 +8626,7 @@
         <v>4.4092488403675549</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F171" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8605,7 +8662,7 @@
         <v>5.2910986084410663</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F172" s="14">
         <f t="shared" si="64"/>
@@ -8639,7 +8696,7 @@
         <v>8.8184976807351099</v>
       </c>
       <c r="E173" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F173" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8747,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F176" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8778,7 +8835,7 @@
       </c>
       <c r="D177" s="21"/>
       <c r="E177" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F177" s="14"/>
       <c r="G177" s="81"/>
@@ -8806,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F178" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8873,7 +8930,7 @@
         <v/>
       </c>
       <c r="E180" s="44" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F180" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8903,7 +8960,7 @@
         <v/>
       </c>
       <c r="E181" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F181" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8963,7 +9020,7 @@
         <v/>
       </c>
       <c r="E183" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F183" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9016,7 +9073,7 @@
       <c r="C185" s="56"/>
       <c r="D185" s="21"/>
       <c r="E185" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F185" s="14"/>
       <c r="G185" s="14"/>
@@ -9151,7 +9208,7 @@
         <v/>
       </c>
       <c r="E190" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F190" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9181,7 +9238,7 @@
         <v/>
       </c>
       <c r="E191" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F191" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9211,7 +9268,7 @@
         <v/>
       </c>
       <c r="E192" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F192" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9331,7 +9388,7 @@
         <v/>
       </c>
       <c r="E196" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F196" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9391,7 +9448,7 @@
         <v/>
       </c>
       <c r="E198" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F198" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9511,7 +9568,7 @@
         <v/>
       </c>
       <c r="E202" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F202" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9541,7 +9598,7 @@
         <v/>
       </c>
       <c r="E203" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F203" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9601,7 +9658,7 @@
         <v/>
       </c>
       <c r="E205" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F205" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9631,7 +9688,7 @@
         <v/>
       </c>
       <c r="E206" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F206" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9669,7 +9726,7 @@
     </row>
     <row r="208" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="124" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C208" s="56"/>
       <c r="D208" s="21"/>
@@ -9691,10 +9748,10 @@
         <v>752.11203019453603</v>
       </c>
       <c r="E209" s="65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F209" s="63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G209" s="64" t="s">
         <v>1</v>
@@ -9889,29 +9946,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B3">
-    <cfRule type="expression" dxfId="8" priority="6">
+    <cfRule type="expression" dxfId="10" priority="8">
       <formula>AND(COUNTBLANK($C$3)=0,$C$3=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B206">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AND($B3="x",AND(COUNTBLANK($C3)=0,$C3=0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C206">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND(COUNTBLANK($C3)=0,$C3=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E216">
-    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
+    <cfRule type="containsText" dxfId="7" priority="3" stopIfTrue="1" operator="containsText" text="~*~*">
       <formula>NOT(ISERROR(SEARCH("~*~*",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="~*">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="~*">
       <formula>NOT(ISERROR(SEARCH("~*",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <conditionalFormatting sqref="N12">
+    <cfRule type="containsText" dxfId="1" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
+      <formula>NOT(ISERROR(SEARCH("~*~*",N12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="~*">
+      <formula>NOT(ISERROR(SEARCH("~*",N12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations disablePrompts="1" count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4" xr:uid="{93D0D4FF-F73B-4CEC-9F59-1E03B78731B5}">
       <formula1>Backpacks</formula1>
     </dataValidation>
@@ -9929,6 +9994,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9" xr:uid="{305C59DD-782B-4B95-B638-F9C3441EC896}">
       <formula1>SleepingBagLiners</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N10" xr:uid="{016C0807-E2D1-4846-99A3-E0F3B38521D2}">
+      <formula1>Tarps</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1"/>
@@ -9972,25 +10040,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" t="str">
         <v>Blue Pack</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D2" t="str">
         <v>pot .7 gt cup &amp; windscreen</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F2" t="str">
         <v>Maps</v>
       </c>
       <c r="G2" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H2" t="str">
         <v>Medication</v>
@@ -9998,25 +10066,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B3" t="str">
         <v>Pack hip pockets</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D3" t="str">
         <v>IsoPro Stove w/ ignitor</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F3" t="str">
         <v>Compass</v>
       </c>
       <c r="G3" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H3" t="str">
         <v>24-32 ounces food per day</v>
@@ -10024,25 +10092,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" t="str">
         <v>Pack Liner/Garbage bag</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D4" t="str">
         <v>IsoPro canister 8oz</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F4" t="str">
         <v>Trail details</v>
       </c>
       <c r="G4" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H4" t="str">
         <v>64 ounces water</v>
@@ -10050,19 +10118,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" t="str">
         <v>Orange Pack Cover</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" t="str">
         <v>IsoPro canister stand</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F5" t="str">
         <v>pen / pencil</v>
@@ -10076,13 +10144,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D6" t="str">
         <v>cozy for freezer bag meals</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F6" t="str">
         <v>notepad / journal</v>
@@ -10097,7 +10165,7 @@
         <v>Shelter Group</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D7" t="str">
         <v>lighter</v>
@@ -10107,7 +10175,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H7" t="str">
         <v>trekking poles</v>
@@ -10115,13 +10183,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" t="str">
         <v>Bridge Hammock; 1.2 Hexon Olive</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D8" t="str">
         <v>spork short</v>
@@ -10131,7 +10199,7 @@
         <v>First Aid Group</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H8" t="str">
         <v>hiking boots</v>
@@ -10139,25 +10207,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" t="str">
         <v>Spreader Bars 28"</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" t="str">
         <v>spoon long</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F9" t="str">
         <v>First aid kit</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9" t="str">
         <v>liner socks</v>
@@ -10165,13 +10233,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B10" t="str">
         <v>Tree straps spider poly</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="str">
         <v>3 liter bladder</v>
@@ -10181,7 +10249,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G10" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H10" t="str">
         <v>wool socks</v>
@@ -10189,13 +10257,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" t="str">
         <v>UCR</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="str">
         <v>water bottles collapsable</v>
@@ -10205,7 +10273,7 @@
         <v>Repair Group</v>
       </c>
       <c r="G11" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H11" t="str">
         <v>gators</v>
@@ -10213,25 +10281,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="str">
         <v>Tarp Forest green &amp; lines</v>
       </c>
       <c r="C12" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D12" t="str">
         <v>smart water bottles</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F12" t="str">
         <v>Tenacious tape</v>
       </c>
       <c r="G12" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H12" t="str">
         <v>tech shirt</v>
@@ -10239,25 +10307,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" t="str">
         <v>stakes AL red</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D13" t="str">
         <v>Water Filter Kit</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F13" t="str">
         <v>Duct tape on trekking poles</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H13" t="str">
         <v>underwear</v>
@@ -10265,25 +10333,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" t="str">
         <v>Tyvek 4x3</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D14" t="str">
         <v xml:space="preserve">  --Filter  (New: Versa Filter)</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F14" t="str">
         <v>extra buckle</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H14" t="str">
         <v>Kilt / Zip-offs</v>
@@ -10291,13 +10359,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B15" t="str">
         <v>Mylar blanket</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D15" t="str">
         <v xml:space="preserve">   --CNOC 3 liter</v>
@@ -10307,7 +10375,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H15" t="str">
         <v>runners cap</v>
@@ -10318,7 +10386,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D16" t="str">
         <v xml:space="preserve">  --tubing</v>
@@ -10328,7 +10396,7 @@
         <v>Misc Group</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H16" t="str">
         <v>pocket knife</v>
@@ -10339,19 +10407,19 @@
         <v>Sleeping Group</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D17" t="str">
         <v xml:space="preserve">  --sawyer squeze</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F17" t="str">
         <v>phone battery 4,000mAh</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H17" t="str">
         <v>lip balm</v>
@@ -10359,25 +10427,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" t="str">
         <v>15° sleeping bag - Katahdin</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D18" t="str">
         <v xml:space="preserve">  --bleach/polar pure/ tablets</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F18" t="str">
         <v>Camp chair - heavy</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H18" t="str">
         <v>phone (in zip-loc)</v>
@@ -10385,25 +10453,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B19" t="str">
         <v>sleeping bag liner blue</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D19" t="str">
         <v>food bag Blue</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F19" t="str">
         <v>hammock chair (green)</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H19" t="str">
         <v>license / money / credit card</v>
@@ -10411,25 +10479,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" t="str">
         <v>pillow black (Outdoor Vitals)</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D20" t="str">
         <v>bear bag and rope</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F20" t="str">
         <v>head lamp</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H20" t="str">
         <v>bandana</v>
@@ -10437,25 +10505,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" t="str">
         <v>Under Quilt Blue 5.0 Climashield</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D21" t="str">
         <v>red bandana</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F21" t="str">
         <v>spare batteries 3 AAA</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H21" t="str">
         <v>belt</v>
@@ -10463,7 +10531,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" t="str">
         <v xml:space="preserve"> </v>
@@ -10473,13 +10541,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F22" t="str">
         <v>rope pieces</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H22" t="str">
         <v>suspenders</v>
@@ -10495,7 +10563,7 @@
         <v>Hygiene Group</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F23" t="str">
         <v>eye glass case - soft</v>
@@ -10507,13 +10575,13 @@
         <v>Down booties</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" t="str">
         <v>Bathroom kit</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F24" t="str">
         <v>foam pad 12 x 18</v>
@@ -10521,13 +10589,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B25" t="str">
         <v>Fleece hat</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" t="str">
         <v xml:space="preserve">  --TP</v>
@@ -10539,13 +10607,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B26" t="str">
         <v>long sleeve shirt</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D26" t="str">
         <v xml:space="preserve">  --wet wipes</v>
@@ -10557,19 +10625,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" t="str">
         <v>underwear</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D27" t="str">
         <v xml:space="preserve">  -- hand sanitizer</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F27" t="str">
         <v>puffy</v>
@@ -10577,19 +10645,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" t="str">
         <v>Wool socks</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D28" t="str">
         <v xml:space="preserve">  --Gold Bond</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F28" t="str">
         <v>gloves/mittens</v>
@@ -10597,19 +10665,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" t="str">
         <v>Liner socks</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D29" t="str">
         <v>Shovel plastic</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F29" t="str">
         <v>Liner socks</v>
@@ -10617,19 +10685,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B30" t="str">
         <v>running tights *</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D30" t="str">
         <v>water jug botom</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F30" t="str">
         <v>Wool socks</v>
@@ -10637,19 +10705,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31" t="str">
         <v>camp shoes</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D31" t="str">
         <v>tooth brush</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F31" t="str">
         <v xml:space="preserve">long sleeve shirt </v>
@@ -10657,19 +10725,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B32" t="str">
         <v xml:space="preserve"> </v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D32" t="str">
         <v>tooth  dots / paste</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F32" t="str">
         <v>underwear</v>
@@ -10680,13 +10748,13 @@
         <v>Rain Gear Group</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D33" t="str">
         <v>hand sanitizer on pack</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F33" t="str">
         <v>shorts</v>
@@ -10701,7 +10769,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F34" t="str">
         <v>zip-offs</v>
@@ -10709,7 +10777,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B35" t="str">
         <v>Rain pants blue FroggTog</v>
@@ -10721,7 +10789,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B36" t="str">
         <v xml:space="preserve"> </v>
@@ -10729,13 +10797,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:H15 B16:H18 A18 A19:H31 A32 B32:H33 A34:H44">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Pounds">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Pounds">
       <formula>NOT(ISERROR(SEARCH("Pounds",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="Ounces">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Ounces">
       <formula>NOT(ISERROR(SEARCH("Ounces",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12751,7 +12819,7 @@
         <v>758.24970458032828</v>
       </c>
       <c r="C131" s="69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D131" s="110"/>
       <c r="E131" s="107"/>
@@ -12767,7 +12835,7 @@
         <v>47</v>
       </c>
       <c r="C132" s="70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D132" s="110"/>
       <c r="E132" s="107"/>
@@ -12782,7 +12850,7 @@
         <v>6.2497045803282845</v>
       </c>
       <c r="C133" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D133" s="110"/>
       <c r="E133" s="107"/>
@@ -12791,7 +12859,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:G124 C131:G151">
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="2" priority="13" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12823,10 +12891,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>1</v>
@@ -12877,7 +12945,7 @@
         <v>1296</v>
       </c>
       <c r="H3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -12927,10 +12995,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -12942,16 +13010,16 @@
         <v>1</v>
       </c>
       <c r="H8" s="85" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I8" s="113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J8" s="113" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="123" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -12976,7 +13044,7 @@
         <v>25.53836928340888</v>
       </c>
       <c r="H9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I9">
         <f>INT(G9/16)</f>
@@ -12995,7 +13063,7 @@
         <v>10.666666666666668</v>
       </c>
       <c r="N9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -13012,7 +13080,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F10">
         <v>193</v>
@@ -13022,7 +13090,7 @@
         <v>6.8078802095275055</v>
       </c>
       <c r="H10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I10">
         <f>INT(G10/16)</f>
@@ -13040,7 +13108,7 @@
         <v>4.0200000000000005</v>
       </c>
       <c r="N10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13064,7 +13132,7 @@
         <v>10.688019189050953</v>
       </c>
       <c r="H11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I11">
         <f>INT(G11/16)</f>
@@ -13100,7 +13168,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="H12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I12">
         <f>INT(G12/16)</f>
@@ -13125,7 +13193,7 @@
         <v>10.970211114834477</v>
       </c>
       <c r="E13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F13">
         <v>37</v>
@@ -13135,7 +13203,7 @@
         <v>1.3051376567487962</v>
       </c>
       <c r="H13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I13">
         <f>INT(G13/16)</f>
@@ -13185,10 +13253,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>1</v>
@@ -13218,7 +13286,7 @@
         <v>17.284255454240817</v>
       </c>
       <c r="H18" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I18">
         <f>INT(G18/16)</f>
@@ -13271,7 +13339,7 @@
         <v>61.976401700206353</v>
       </c>
       <c r="H21" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="I21">
         <f>INT(G21/16)</f>
@@ -13284,10 +13352,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C22" s="86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>1</v>
@@ -13393,12 +13461,12 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
@@ -13407,16 +13475,16 @@
         <v>1</v>
       </c>
       <c r="I30" s="113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J30" s="113" t="s">
         <v>1</v>
       </c>
       <c r="M30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O30" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -13435,7 +13503,7 @@
       </c>
       <c r="J31" s="9"/>
       <c r="L31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="M31">
         <v>0.9</v>
@@ -13472,7 +13540,7 @@
         <v>28.166666666666664</v>
       </c>
       <c r="H32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I32">
         <f t="shared" ref="I32:I33" si="0">INT(G32/16)</f>
@@ -13525,7 +13593,7 @@
         <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -13578,7 +13646,7 @@
         <v>54.166666666666664</v>
       </c>
       <c r="H34" s="116" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="I34" s="116">
         <f>SUM(I32:I33)</f>
@@ -13610,7 +13678,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="H35" s="117" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I35" s="117">
         <f>INT(G35/16)</f>
@@ -13621,7 +13689,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="K35" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -13643,7 +13711,7 @@
         <v>1.6931515547011413</v>
       </c>
       <c r="H36" s="120" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I36" s="120">
         <f>INT(G36/16)</f>
@@ -13687,7 +13755,7 @@
         <v>22.313333333333325</v>
       </c>
       <c r="H38" s="122" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I38" s="122">
         <f t="shared" ref="I38" si="3">INT(G38/16)</f>
@@ -13698,7 +13766,7 @@
         <v>6.3133333333333255</v>
       </c>
       <c r="L38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -13706,7 +13774,7 @@
         <v>25.079807404010655</v>
       </c>
       <c r="B39" t="str">
-        <v>Air matress Big Birtha</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -13718,7 +13786,7 @@
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -13738,7 +13806,7 @@
         <v>3.6</v>
       </c>
       <c r="M40" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -13758,7 +13826,7 @@
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -13778,7 +13846,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -13798,7 +13866,7 @@
         <v>7.5</v>
       </c>
       <c r="M43" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -13807,7 +13875,7 @@
         <v>76.47999999999999</v>
       </c>
       <c r="B45" s="116" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C45" s="116">
         <f t="shared" ref="C45" si="5">INT(A45/16)</f>

--- a/AT/GearListNew.xlsx
+++ b/AT/GearListNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1194" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4013FAE-664E-4B0F-83A0-0555F1E70A6D}"/>
+  <xr:revisionPtr revIDLastSave="1195" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B575C0-2620-4F9F-A622-B5A716DA572C}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="840" windowWidth="27435" windowHeight="14730" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
+    <workbookView xWindow="1230" yWindow="855" windowWidth="27525" windowHeight="15225" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gear Checklist" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -117,9 +117,6 @@
   </si>
   <si>
     <t>Maps</t>
-  </si>
-  <si>
-    <t>bear bag and rope</t>
   </si>
   <si>
     <t>Trail details</t>
@@ -961,6 +958,9 @@
   </si>
   <si>
     <t>Selection Name</t>
+  </si>
+  <si>
+    <t>bag and rope</t>
   </si>
 </sst>
 </file>
@@ -1663,20 +1663,9 @@
   <dxfs count="11">
     <dxf>
       <font>
-        <color auto="1"/>
+        <b/>
+        <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1698,9 +1687,20 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <color auto="1"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2093,24 +2093,24 @@
         <v>17</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F1" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B2" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>53</v>
-      </c>
       <c r="E2" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>1</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L2" s="26"/>
       <c r="M2" s="35"/>
@@ -2143,40 +2143,40 @@
     <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="18"/>
       <c r="B3" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="76" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="44" t="s">
-        <v>54</v>
-      </c>
       <c r="F3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K3" s="26"/>
       <c r="L3" s="26"/>
       <c r="M3" s="35"/>
       <c r="N3" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O3" s="40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P3" s="26"/>
       <c r="Q3" s="27"/>
@@ -2186,10 +2186,10 @@
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="77">
         <v>1290</v>
@@ -2199,7 +2199,7 @@
         <v>45.50344803259317</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="20">
         <f>IF(B4="x",IF(C4=0,"",C4),"")</f>
@@ -2228,10 +2228,10 @@
         <v>41.446939099455015</v>
       </c>
       <c r="N4" s="125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
@@ -2249,7 +2249,7 @@
         <v>41.446939099455015</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F5" s="20" t="str">
         <f t="shared" ref="F5:F64" si="1">IF(B5="x",IF(C5=0,"",C5),"")</f>
@@ -2277,10 +2277,10 @@
         <v>5.1500026455493044</v>
       </c>
       <c r="N5" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O5" s="25" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2319,7 +2319,7 @@
         <v>Griz Arieal Hammock; 1.2ox Hexon; Dak Olive</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="21" cm="1">
@@ -2327,10 +2327,10 @@
         <v>8.2188398384451222</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2375,10 +2375,10 @@
         <v>17.213707472794937</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P7" s="25"/>
       <c r="Q7" s="25"/>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2423,10 +2423,10 @@
         <v>38.378101906559202</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P8" s="25"/>
       <c r="Q8" s="25"/>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="9" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="59">
         <v>27</v>
@@ -2449,7 +2449,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="20">
         <f t="shared" si="1"/>
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O9" s="25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P9" s="25"/>
       <c r="Q9" s="25"/>
@@ -2490,10 +2490,10 @@
     </row>
     <row r="10" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="56">
         <v>143</v>
@@ -2503,7 +2503,7 @@
         <v>5.0441806733804828</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="20">
         <f t="shared" si="1"/>
@@ -2531,10 +2531,10 @@
         <v>16.71987160267377</v>
       </c>
       <c r="N10" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P10" s="25"/>
       <c r="Q10" s="25"/>
@@ -2552,7 +2552,7 @@
         <v>7.0547981445880881</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2586,10 +2586,10 @@
     </row>
     <row r="12" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="56">
         <v>146</v>
@@ -2599,7 +2599,7 @@
         <v>5.1500026455493044</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12" s="20">
         <f t="shared" si="1"/>
@@ -2639,7 +2639,7 @@
         <v/>
       </c>
       <c r="E13" s="31" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F13" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2661,7 +2661,7 @@
         <v>Ultralight chair</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L13" s="20"/>
       <c r="M13" s="21"/>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="14" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="99">
         <f>SUMIF(B4:B13,"x",F4:F13)</f>
@@ -2686,7 +2686,7 @@
         <v>56.65002910104235</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" s="20">
         <f t="shared" si="1"/>
@@ -2719,7 +2719,7 @@
     <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="21" t="str">
@@ -2727,10 +2727,10 @@
         <v/>
       </c>
       <c r="E15" s="44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G15" s="21" t="str">
         <f t="shared" si="2"/>
@@ -2766,7 +2766,7 @@
         <v>13.545212437609129</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F16" s="20" t="str">
         <f t="shared" si="1"/>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="17" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="56">
         <v>233</v>
@@ -2811,7 +2811,7 @@
         <v>8.2188398384451222</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F17" s="20">
         <f t="shared" si="1"/>
@@ -2849,7 +2849,7 @@
         <v/>
       </c>
       <c r="E18" s="114" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F18" s="20" t="str">
         <f t="shared" ref="F18:F19" si="6">IF(B18="x",IF(C18=0,"",C18),"")</f>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J18" s="25"/>
       <c r="K18" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L18" s="20"/>
       <c r="M18" s="21"/>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="20" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="56">
         <v>207</v>
@@ -2932,7 +2932,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F20" s="20">
         <f t="shared" ref="F20:F21" si="10">IF(B20="x",IF(C20=0,"",C20),"")</f>
@@ -2971,7 +2971,7 @@
         <v>7.9719219033845397</v>
       </c>
       <c r="E21" s="80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F21" s="20" t="str">
         <f t="shared" si="10"/>
@@ -3011,7 +3011,7 @@
         <v>3.4215771001252229</v>
       </c>
       <c r="E22" s="45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="23" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="56">
         <v>82</v>
@@ -3056,7 +3056,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F23" s="20">
         <f t="shared" si="1"/>
@@ -3075,7 +3075,7 @@
         <v>2.8924672392811162</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
@@ -3098,7 +3098,7 @@
         <v>1.4109596289176176</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="25" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="56">
         <v>40</v>
@@ -3143,7 +3143,7 @@
         <v>1.4109596289176176</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F25" s="20">
         <f t="shared" si="1"/>
@@ -3183,7 +3183,7 @@
         <v>26.45549304220533</v>
       </c>
       <c r="E26" s="45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F26" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="56">
         <v>474</v>
@@ -3228,7 +3228,7 @@
         <v>16.71987160267377</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F27" s="20">
         <v>300</v>
@@ -3246,7 +3246,7 @@
         <v>0.71987160267376993</v>
       </c>
       <c r="J27" s="67" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="28" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="56">
         <v>80</v>
@@ -3274,7 +3274,7 @@
         <v>2.8219192578352352</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F28" s="20">
         <f t="shared" si="1"/>
@@ -3314,7 +3314,7 @@
         <v>4.0565089331381508</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="30" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C30" s="56">
         <v>126</v>
@@ -3356,7 +3356,7 @@
         <v>4.4445228310904952</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="31" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C31" s="56">
         <v>311</v>
@@ -3398,7 +3398,7 @@
         <v>10.970211114834477</v>
       </c>
       <c r="E31" s="45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F31" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3430,7 +3430,7 @@
     </row>
     <row r="32" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32" s="56">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F32" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3459,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K32" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L32" s="20"/>
       <c r="M32" s="21"/>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="33" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C33" s="56">
         <v>545</v>
@@ -3486,7 +3486,7 @@
         <v>19.224324944002539</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="34" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C34" s="56">
         <v>305</v>
@@ -3528,7 +3528,7 @@
         <v>10.758567170496834</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3560,7 +3560,7 @@
     </row>
     <row r="35" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="56">
         <v>71</v>
@@ -3570,7 +3570,7 @@
         <v>2.5044533413287713</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="20">
         <f t="shared" si="1"/>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="36" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="56">
@@ -3613,7 +3613,7 @@
         <v>4.1976048960299126</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F36" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3653,7 +3653,7 @@
         <v>6.878428190973386</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F37" s="14" t="str">
         <f t="shared" si="1"/>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F38" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="39" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="56">
         <v>39</v>
@@ -3734,7 +3734,7 @@
         <v>1.3756856381946772</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F39" s="20">
         <f t="shared" si="1"/>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="40" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="99">
         <f>SUMIF(B16:B39,"x",F16:F39)</f>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="41" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="56"/>
       <c r="D41" s="21" t="str">
@@ -3814,7 +3814,7 @@
         <v/>
       </c>
       <c r="E41" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F41" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="42" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" s="56">
         <v>1088</v>
@@ -3856,7 +3856,7 @@
         <v>38.378101906559202</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="43" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="56">
         <v>1270</v>
@@ -3898,7 +3898,7 @@
         <v>44.797968218134358</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F43" s="20">
         <f t="shared" si="1"/>
@@ -3938,7 +3938,7 @@
         <v>55.203795481401791</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F44" s="20" t="str">
         <f t="shared" si="1"/>
@@ -3978,7 +3978,7 @@
         <v>38.413375897282137</v>
       </c>
       <c r="E45" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" s="20" t="str">
         <f t="shared" ref="F45" si="12">IF(B45="x",IF(C45=0,"",C45),"")</f>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="46" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="56">
         <v>176</v>
@@ -4020,7 +4020,7 @@
         <v>6.2082223672375179</v>
       </c>
       <c r="E46" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" s="20">
         <f t="shared" si="1"/>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F47" s="20" t="str">
         <f t="shared" ref="F47" si="14">IF(B47="x",IF(C47=0,"",C47),"")</f>
@@ -4078,10 +4078,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L47" s="14"/>
       <c r="M47" s="21"/>
@@ -4103,7 +4103,7 @@
         <v>3.033563202172878</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" s="20" t="str">
         <f t="shared" ref="F48" si="17">IF(B48="x",IF(C48=0,"",C48),"")</f>
@@ -4135,7 +4135,7 @@
     </row>
     <row r="49" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B49" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="56">
         <v>90</v>
@@ -4145,7 +4145,7 @@
         <v>3.1746591650646399</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F49" s="20">
         <f t="shared" ref="F49" si="19">IF(B49="x",IF(C49=0,"",C49),"")</f>
@@ -4184,7 +4184,7 @@
         <v>25.079807404010655</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F50" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4216,7 +4216,7 @@
     </row>
     <row r="51" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="56">
@@ -4227,7 +4227,7 @@
         <v>17.213707472794937</v>
       </c>
       <c r="E51" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F51" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F52" s="20" t="str">
         <f t="shared" ref="F52" si="21">IF(B52="x",IF(C52=0,"",C52),"")</f>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="J52" s="25"/>
       <c r="K52" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L52" s="20"/>
       <c r="M52" s="21"/>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="53" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="56">
         <v>898</v>
@@ -4307,7 +4307,7 @@
         <v>31.676043669200517</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F53" s="20">
         <f t="shared" si="1"/>
@@ -4326,7 +4326,7 @@
         <v>15.676043669200517</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K53" s="20"/>
       <c r="L53" s="20"/>
@@ -4343,7 +4343,7 @@
       <c r="C54" s="56"/>
       <c r="D54" s="21"/>
       <c r="E54" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="21"/>
@@ -4351,7 +4351,7 @@
       <c r="I54" s="21"/>
       <c r="J54" s="25"/>
       <c r="K54" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L54" s="20"/>
       <c r="M54" s="21"/>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="55" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B55" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="99">
         <f>SUMIF(B42:B53,"x",F42:F53)</f>
@@ -4376,7 +4376,7 @@
         <v>85.856893419637032</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" s="20">
         <f t="shared" ref="F55:F57" si="23">IF(B55="x",IF(C55=0,"",C55),"")</f>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="56" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B56" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="56"/>
       <c r="D56" s="21" t="str">
@@ -4416,7 +4416,7 @@
         <v/>
       </c>
       <c r="E56" s="27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F56" s="20" t="str">
         <f t="shared" si="23"/>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="57" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B57" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="56">
         <v>84</v>
@@ -4458,7 +4458,7 @@
         <v>2.9630152207269971</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F57" s="20">
         <f t="shared" si="23"/>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="58" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B58" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="56">
         <v>93</v>
@@ -4500,7 +4500,7 @@
         <v>3.280481137233461</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F58" s="20">
         <f t="shared" si="1"/>
@@ -4539,7 +4539,7 @@
         <v>1.0934937124111537</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F59" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4578,7 +4578,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F60" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="61" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B61" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="56">
         <v>148</v>
@@ -4620,7 +4620,7 @@
         <v>5.2205506269951849</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F61" s="20">
         <f t="shared" si="1"/>
@@ -4659,7 +4659,7 @@
         <v>4.6561667754281384</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F62" s="20" t="str">
         <f t="shared" si="1"/>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="63" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B63" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="56">
         <v>76</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="64" spans="1:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B64" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="56">
         <v>166</v>
@@ -4743,7 +4743,7 @@
         <v>5.8554824600081128</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F64" s="14">
         <f t="shared" si="1"/>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="65" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B65" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C65" s="56">
         <v>47</v>
@@ -4785,7 +4785,7 @@
         <v>1.6578775639782006</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F65" s="14">
         <f t="shared" ref="F65" si="25">IF(B65="x",IF(C65=0,"",C65),"")</f>
@@ -4817,7 +4817,7 @@
     </row>
     <row r="66" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B66" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" s="56">
         <v>188</v>
@@ -4827,7 +4827,7 @@
         <v>6.6315102559128025</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F66" s="14">
         <f t="shared" ref="F66:F79" si="27">IF(B66="x",IF(C66=0,"",C66),"")</f>
@@ -4866,7 +4866,7 @@
         <v>4.4092488403675549</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67" s="14" t="str">
         <f t="shared" si="27"/>
@@ -4905,7 +4905,7 @@
         <v>1.6226035732552604</v>
       </c>
       <c r="E68" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" s="14" t="str">
         <f t="shared" si="27"/>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="69" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B69" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="56">
         <v>385</v>
@@ -4947,7 +4947,7 @@
         <v>13.580486428332069</v>
       </c>
       <c r="E69" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F69" s="14">
         <f t="shared" si="27"/>
@@ -4979,7 +4979,7 @@
     </row>
     <row r="70" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B70" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C70" s="99">
         <f>SUMIF(B57:B69,"x",C57:C69)</f>
@@ -4990,7 +4990,7 @@
         <v>41.870226988130305</v>
       </c>
       <c r="E70" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F70" s="14">
         <f t="shared" ref="F70" si="29">IF(B70="x",IF(C70=0,"",C70),"")</f>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="71" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C71" s="56"/>
       <c r="D71" s="21" t="str">
@@ -5030,7 +5030,7 @@
         <v/>
       </c>
       <c r="E71" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F71" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5062,7 +5062,7 @@
     </row>
     <row r="72" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B72" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C72" s="56">
         <v>244</v>
@@ -5072,7 +5072,7 @@
         <v>8.6068537363974684</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F72" s="14">
         <f t="shared" si="27"/>
@@ -5112,7 +5112,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F73" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5131,7 +5131,7 @@
         <v>15.661651880985556</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K73" s="20"/>
       <c r="L73" s="20"/>
@@ -5154,7 +5154,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="E74" s="45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F74" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5173,7 +5173,7 @@
         <v>10.582197216882133</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K74" s="20"/>
       <c r="L74" s="20"/>
@@ -5196,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="45" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F75" s="14" t="str">
         <f t="shared" si="27"/>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="76" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B76" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C76" s="56">
         <v>129</v>
@@ -5238,7 +5238,7 @@
         <v>4.5503448032593168</v>
       </c>
       <c r="E76" s="45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F76" s="14">
         <f t="shared" ref="F76" si="33">IF(B76="x",IF(C76=0,"",C76),"")</f>
@@ -5277,7 +5277,7 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="E77" s="46" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F77" s="14" t="str">
         <f t="shared" ref="F77" si="35">IF(B77="x",IF(C77=0,"",C77),"")</f>
@@ -5296,10 +5296,10 @@
         <v>2.5750013227746522</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K77" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L77" s="20"/>
       <c r="M77" s="21"/>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="79" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B79" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C79" s="99">
         <f>SUMIF(B72:B78,"x",C72:C78)</f>
@@ -5364,7 +5364,7 @@
         <v>13.157198539656784</v>
       </c>
       <c r="E79" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F79" s="14">
         <f t="shared" si="27"/>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="80" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B80" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C80" s="56"/>
       <c r="D80" s="21" t="str">
@@ -5404,7 +5404,7 @@
         <v/>
       </c>
       <c r="E80" s="44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F80" s="14" t="str">
         <f t="shared" ref="F80:F151" si="37">IF(B80="x",IF(C80=0,"",C80),"")</f>
@@ -5423,7 +5423,7 @@
         <v/>
       </c>
       <c r="J80" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K80" s="20"/>
       <c r="L80" s="20"/>
@@ -5445,7 +5445,7 @@
         <v>4.3034268681987342</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F81" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5477,7 +5477,7 @@
     </row>
     <row r="82" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B82" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C82" s="56">
         <v>78</v>
@@ -5487,7 +5487,7 @@
         <v>2.7513712763893543</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F82" s="14">
         <f t="shared" si="37"/>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="83" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B83" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C83" s="56">
         <v>110</v>
@@ -5529,7 +5529,7 @@
         <v>3.8801389795234487</v>
       </c>
       <c r="E83" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F83" s="14">
         <f t="shared" si="37"/>
@@ -5569,7 +5569,7 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="E84" s="46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F84" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5588,10 +5588,10 @@
         <v>0.88184976807351101</v>
       </c>
       <c r="J84" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K84" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L84" s="20"/>
       <c r="M84" s="21"/>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F85" s="14" t="str">
         <f t="shared" si="37"/>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="86" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B86" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C86" s="56">
         <v>227</v>
@@ -5655,7 +5655,7 @@
         <v>8.0071958941074808</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F86" s="14">
         <f t="shared" si="37"/>
@@ -5695,7 +5695,7 @@
         <v>4.0212349424152105</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F87" s="14" t="str">
         <f t="shared" ref="F87" si="40">IF(B87="x",IF(C87=0,"",C87),"")</f>
@@ -5735,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F88" s="14" t="str">
         <f t="shared" ref="F88:F97" si="42">IF(B88="x",IF(C88=0,"",C88),"")</f>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="89" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B89" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C89" s="56">
         <v>27</v>
@@ -5777,7 +5777,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F89" s="14">
         <f t="shared" si="42"/>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="90" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B90" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C90" s="56">
         <v>26</v>
@@ -5819,7 +5819,7 @@
         <v>0.91712375879645147</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F90" s="14">
         <f t="shared" si="42"/>
@@ -5851,7 +5851,7 @@
     </row>
     <row r="91" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B91" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C91" s="56">
         <v>30</v>
@@ -5861,7 +5861,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E91" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F91" s="14">
         <f t="shared" si="42"/>
@@ -5901,7 +5901,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E92" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F92" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5941,7 +5941,7 @@
         <v>0.4938358701211662</v>
       </c>
       <c r="E93" s="25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F93" s="14" t="str">
         <f t="shared" si="42"/>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="94" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B94" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C94" s="56">
         <v>10</v>
@@ -5983,7 +5983,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F94" s="14">
         <f t="shared" si="42"/>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="95" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B95" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C95" s="56">
         <v>10</v>
@@ -6025,7 +6025,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F95" s="14">
         <f t="shared" si="42"/>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="96" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B96" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C96" s="56">
         <v>209</v>
@@ -6067,7 +6067,7 @@
         <v>7.372264061094552</v>
       </c>
       <c r="E96" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F96" s="14">
         <f t="shared" si="42"/>
@@ -6099,7 +6099,7 @@
     </row>
     <row r="97" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B97" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C97" s="56">
         <v>35</v>
@@ -6109,7 +6109,7 @@
         <v>1.2345896753029155</v>
       </c>
       <c r="E97" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F97" s="14">
         <f t="shared" si="42"/>
@@ -6141,7 +6141,7 @@
     </row>
     <row r="98" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B98" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C98" s="56">
         <v>30</v>
@@ -6151,7 +6151,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F98" s="14">
         <f t="shared" ref="F98" si="44">IF(B98="x",IF(C98=0,"",C98),"")</f>
@@ -6183,7 +6183,7 @@
     </row>
     <row r="99" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B99" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C99" s="56">
         <v>286</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="100" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B100" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C100" s="56"/>
       <c r="D100" s="21" t="str">
@@ -6233,7 +6233,7 @@
         <v/>
       </c>
       <c r="E100" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F100" s="14"/>
       <c r="G100" s="81"/>
@@ -6246,7 +6246,7 @@
         <v/>
       </c>
       <c r="J100" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
@@ -6261,7 +6261,7 @@
     </row>
     <row r="101" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B101" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C101" s="56"/>
       <c r="D101" s="21" t="str">
@@ -6269,7 +6269,7 @@
         <v/>
       </c>
       <c r="E101" s="48" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F101" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="102" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B102" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C102" s="56"/>
       <c r="D102" s="21" t="str">
@@ -6309,7 +6309,7 @@
         <v/>
       </c>
       <c r="E102" s="48" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F102" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="103" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B103" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103" s="56"/>
       <c r="D103" s="21" t="str">
@@ -6349,7 +6349,7 @@
         <v/>
       </c>
       <c r="E103" s="48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F103" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="104" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B104" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C104" s="56"/>
       <c r="D104" s="21" t="str">
@@ -6389,7 +6389,7 @@
         <v/>
       </c>
       <c r="E104" s="48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F104" s="14" t="str">
         <f t="shared" si="46"/>
@@ -6429,7 +6429,7 @@
         <v>1.6226035732552604</v>
       </c>
       <c r="E105" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F105" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="106" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B106" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C106" s="56">
         <v>41</v>
@@ -6471,7 +6471,7 @@
         <v>1.4462336196405581</v>
       </c>
       <c r="E106" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F106" s="14">
         <f t="shared" si="37"/>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="107" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B107" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C107" s="56">
         <v>32</v>
@@ -6513,7 +6513,7 @@
         <v>1.1287677031340941</v>
       </c>
       <c r="E107" s="25" t="s">
-        <v>15</v>
+        <v>271</v>
       </c>
       <c r="F107" s="14">
         <f t="shared" si="37"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="108" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B108" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C108" s="56">
         <v>21</v>
@@ -6596,7 +6596,7 @@
         <v>41.341117127286196</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F109" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6626,7 +6626,7 @@
     </row>
     <row r="110" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B110" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C110" s="56"/>
       <c r="D110" s="21" t="str">
@@ -6634,7 +6634,7 @@
         <v/>
       </c>
       <c r="E110" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F110" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="111" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B111" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C111" s="56"/>
       <c r="D111" s="21" t="str">
@@ -6673,7 +6673,7 @@
         <v/>
       </c>
       <c r="E111" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F111" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="112" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B112" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C112" s="56">
         <v>181</v>
@@ -6747,7 +6747,7 @@
     </row>
     <row r="113" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B113" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C113" s="56"/>
       <c r="D113" s="21" t="str">
@@ -6755,7 +6755,7 @@
         <v/>
       </c>
       <c r="E113" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F113" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="114" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B114" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C114" s="56"/>
       <c r="D114" s="21" t="str">
@@ -6795,7 +6795,7 @@
         <v/>
       </c>
       <c r="E114" s="53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F114" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="115" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B115" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C115" s="56"/>
       <c r="D115" s="21" t="str">
@@ -6830,7 +6830,7 @@
         <v/>
       </c>
       <c r="E115" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F115" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="116" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B116" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C116" s="56"/>
       <c r="D116" s="21" t="str">
@@ -6864,7 +6864,7 @@
         <v/>
       </c>
       <c r="E116" s="53" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F116" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6898,7 +6898,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="E117" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F117" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6924,7 +6924,7 @@
     </row>
     <row r="118" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B118" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C118" s="56">
         <v>52</v>
@@ -6934,7 +6934,7 @@
         <v>1.8342475175929029</v>
       </c>
       <c r="E118" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F118" s="14">
         <f t="shared" si="37"/>
@@ -6966,7 +6966,7 @@
         <v>0.74075380518174927</v>
       </c>
       <c r="E119" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F119" s="14" t="str">
         <f t="shared" si="37"/>
@@ -6988,7 +6988,7 @@
     </row>
     <row r="120" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B120" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C120" s="56">
         <v>28</v>
@@ -6998,7 +6998,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E120" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F120" s="14">
         <f t="shared" si="37"/>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="121" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B121" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C121" s="56">
         <v>23</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="122" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B122" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C122" s="56">
         <v>22</v>
@@ -7062,7 +7062,7 @@
         <v>0.77602779590468973</v>
       </c>
       <c r="E122" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F122" s="14">
         <f t="shared" si="37"/>
@@ -7092,7 +7092,7 @@
         <v>2.1517134340993671</v>
       </c>
       <c r="E123" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F123" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7114,7 +7114,7 @@
     </row>
     <row r="124" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B124" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C124" s="56">
         <v>30</v>
@@ -7124,7 +7124,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E124" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F124" s="14">
         <f t="shared" si="37"/>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="125" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B125" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C125" s="99">
         <f>SUMIF(B112:B124,"x",C112:C124)</f>
@@ -7157,7 +7157,7 @@
         <v>11.852060882907988</v>
       </c>
       <c r="E125" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F125" s="14">
         <f t="shared" si="37"/>
@@ -7179,7 +7179,7 @@
     </row>
     <row r="126" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B126" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C126" s="56"/>
       <c r="D126" s="21" t="str">
@@ -7187,7 +7187,7 @@
         <v/>
       </c>
       <c r="E126" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F126" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="127" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B127" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C127" s="56"/>
       <c r="D127" s="21" t="str">
@@ -7239,7 +7239,7 @@
     </row>
     <row r="128" spans="2:20" ht="15" x14ac:dyDescent="0.25">
       <c r="B128" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C128" s="56">
         <v>28</v>
@@ -7249,7 +7249,7 @@
         <v>0.9876717402423324</v>
       </c>
       <c r="E128" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F128" s="14">
         <f t="shared" si="37"/>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="129" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B129" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C129" s="56"/>
       <c r="D129" s="21" t="str">
@@ -7279,7 +7279,7 @@
         <v/>
       </c>
       <c r="E129" s="25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F129" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7301,7 +7301,7 @@
     </row>
     <row r="130" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B130" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C130" s="56">
         <v>9</v>
@@ -7311,7 +7311,7 @@
         <v>0.317465916506464</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F130" s="14">
         <f t="shared" si="37"/>
@@ -7333,7 +7333,7 @@
     </row>
     <row r="131" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B131" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C131" s="56">
         <v>236</v>
@@ -7343,7 +7343,7 @@
         <v>8.3246618106139447</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F131" s="14">
         <f t="shared" si="37"/>
@@ -7365,7 +7365,7 @@
     </row>
     <row r="132" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B132" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C132" s="99">
         <f>SUMIF(B127:B131,"x",C127:C131)</f>
@@ -7376,7 +7376,7 @@
         <v>9.6297994673627407</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F132" s="14">
         <f t="shared" si="37"/>
@@ -7398,7 +7398,7 @@
     </row>
     <row r="133" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B133" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C133" s="56"/>
       <c r="D133" s="21" t="str">
@@ -7406,7 +7406,7 @@
         <v/>
       </c>
       <c r="E133" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F133" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7428,7 +7428,7 @@
     </row>
     <row r="134" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B134" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C134" s="56">
         <v>160</v>
@@ -7438,7 +7438,7 @@
         <v>5.6438385156704705</v>
       </c>
       <c r="E134" s="66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F134" s="14">
         <f t="shared" si="37"/>
@@ -7466,7 +7466,7 @@
         <v/>
       </c>
       <c r="E135" s="66" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F135" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7494,7 +7494,7 @@
         <v/>
       </c>
       <c r="E136" s="66" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F136" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7516,7 +7516,7 @@
     </row>
     <row r="137" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B137" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C137" s="56"/>
       <c r="D137" s="21" t="str">
@@ -7524,7 +7524,7 @@
         <v/>
       </c>
       <c r="E137" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F137" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7546,7 +7546,7 @@
     </row>
     <row r="138" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B138" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C138" s="56"/>
       <c r="D138" s="21" t="str">
@@ -7554,7 +7554,7 @@
         <v/>
       </c>
       <c r="E138" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F138" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7576,7 +7576,7 @@
     </row>
     <row r="139" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B139" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C139" s="56">
         <v>12</v>
@@ -7586,7 +7586,7 @@
         <v>0.42328788867528527</v>
       </c>
       <c r="E139" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F139" s="14">
         <f t="shared" si="37"/>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="140" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B140" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C140" s="56"/>
       <c r="D140" s="21" t="str">
@@ -7616,7 +7616,7 @@
         <v/>
       </c>
       <c r="E140" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F140" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="141" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B141" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C141" s="56">
         <v>38</v>
@@ -7648,7 +7648,7 @@
         <v>1.3404116474717367</v>
       </c>
       <c r="E141" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F141" s="14">
         <f t="shared" si="37"/>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="142" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B142" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C142" s="99">
         <f>SUMIF(B139:B141,"x",C139:C141)</f>
@@ -7681,7 +7681,7 @@
         <v>1.763699536147022</v>
       </c>
       <c r="E142" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F142" s="14">
         <f t="shared" si="37"/>
@@ -7703,7 +7703,7 @@
     </row>
     <row r="143" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B143" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C143" s="56"/>
       <c r="D143" s="21" t="str">
@@ -7711,7 +7711,7 @@
         <v/>
       </c>
       <c r="E143" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F143" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7745,7 +7745,7 @@
         <v>6.5256882837439818</v>
       </c>
       <c r="E144" s="58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F144" s="58" t="str">
         <f t="shared" si="37"/>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="145" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B145" s="55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C145" s="56">
         <v>135</v>
@@ -7777,7 +7777,7 @@
         <v>4.7619887475969591</v>
       </c>
       <c r="E145" s="58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F145" s="58">
         <f t="shared" ref="F145" si="56">IF(B145="x",IF(C145=0,"",C145),"")</f>
@@ -7807,7 +7807,7 @@
         <v>16.931515547011411</v>
       </c>
       <c r="E146" s="50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F146" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="J146" s="25"/>
     </row>
-    <row r="147" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B147" s="18"/>
       <c r="C147" s="56">
         <v>510</v>
@@ -7837,7 +7837,7 @@
         <v>17.989735268699626</v>
       </c>
       <c r="E147" s="61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F147" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7856,15 +7856,15 @@
         <v>1.9897352686996257</v>
       </c>
       <c r="J147" s="67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K147" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="148" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B148" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C148" s="56">
         <v>1000</v>
@@ -7874,7 +7874,7 @@
         <v>35.273990722940439</v>
       </c>
       <c r="E148" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F148" s="14">
         <f t="shared" si="37"/>
@@ -7896,7 +7896,7 @@
     </row>
     <row r="149" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B149" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C149" s="56">
         <v>131</v>
@@ -7906,7 +7906,7 @@
         <v>4.6208927847051982</v>
       </c>
       <c r="E149" s="50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F149" s="14">
         <f t="shared" si="37"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="150" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B150" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C150" s="56">
         <v>69</v>
@@ -7969,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F151" s="14" t="str">
         <f t="shared" si="37"/>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="152" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B152" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C152" s="56">
         <v>36</v>
@@ -8001,7 +8001,7 @@
         <v>1.269863666025856</v>
       </c>
       <c r="E152" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F152" s="14">
         <f t="shared" ref="F152:F162" si="58">IF(B152="x",IF(C152=0,"",C152),"")</f>
@@ -8033,7 +8033,7 @@
         <v>2.539727332051712</v>
       </c>
       <c r="E153" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F153" s="14" t="str">
         <f t="shared" ref="F153" si="61">IF(B153="x",IF(C153=0,"",C153),"")</f>
@@ -8064,7 +8064,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E154" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F154" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8086,7 +8086,7 @@
     </row>
     <row r="155" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B155" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C155" s="56">
         <v>30</v>
@@ -8096,7 +8096,7 @@
         <v>1.0582197216882132</v>
       </c>
       <c r="E155" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F155" s="14">
         <f t="shared" si="58"/>
@@ -8117,7 +8117,7 @@
     </row>
     <row r="156" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B156" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C156" s="56">
         <v>20</v>
@@ -8127,7 +8127,7 @@
         <v>0.70547981445880881</v>
       </c>
       <c r="E156" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F156" s="14">
         <f t="shared" si="58"/>
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="E157" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F157" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="E158" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F158" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="E159" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F159" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8250,7 +8250,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F160" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8273,7 +8273,7 @@
     </row>
     <row r="161" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B161" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C161" s="56">
         <v>49</v>
@@ -8283,7 +8283,7 @@
         <v>1.7284255454240816</v>
       </c>
       <c r="E161" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F161" s="14">
         <f t="shared" si="58"/>
@@ -8313,7 +8313,7 @@
         <v>3.3157551279564013</v>
       </c>
       <c r="E162" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F162" s="14" t="str">
         <f t="shared" si="58"/>
@@ -8343,7 +8343,7 @@
         <v>3.1041111836187589</v>
       </c>
       <c r="E163" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F163" s="14" t="str">
         <f t="shared" ref="F163:F206" si="64">IF(B163="x",IF(C163=0,"",C163),"")</f>
@@ -8369,7 +8369,7 @@
     </row>
     <row r="164" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B164" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C164" s="99">
         <f>SUMIF(B145:B163,"x",C144:C163)</f>
@@ -8380,7 +8380,7 @@
         <v>66.526746503465674</v>
       </c>
       <c r="E164" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F164" s="14">
         <f t="shared" si="64"/>
@@ -8406,7 +8406,7 @@
     </row>
     <row r="165" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B165" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C165" s="56"/>
       <c r="D165" s="21" t="str">
@@ -8414,7 +8414,7 @@
         <v/>
       </c>
       <c r="E165" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F165" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8440,7 +8440,7 @@
     </row>
     <row r="166" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B166" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C166" s="56">
         <v>322</v>
@@ -8450,7 +8450,7 @@
         <v>11.358225012786821</v>
       </c>
       <c r="E166" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F166" s="14">
         <f t="shared" si="64"/>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="167" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B167" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C167" s="56">
         <v>108</v>
@@ -8486,7 +8486,7 @@
         <v>3.8095909980775677</v>
       </c>
       <c r="E167" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F167" s="14">
         <f t="shared" si="64"/>
@@ -8520,7 +8520,7 @@
         <v>1.269863666025856</v>
       </c>
       <c r="E168" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F168" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="169" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B169" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C169" s="56">
         <v>50</v>
@@ -8556,7 +8556,7 @@
         <v>1.763699536147022</v>
       </c>
       <c r="E169" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F169" s="14">
         <f t="shared" si="64"/>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="170" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B170" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C170" s="56">
         <v>165</v>
@@ -8592,7 +8592,7 @@
         <v>5.8202084692851725</v>
       </c>
       <c r="E170" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F170" s="14">
         <f t="shared" si="64"/>
@@ -8626,7 +8626,7 @@
         <v>4.4092488403675549</v>
       </c>
       <c r="E171" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F171" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8652,7 +8652,7 @@
     </row>
     <row r="172" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B172" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C172" s="56">
         <v>150</v>
@@ -8662,7 +8662,7 @@
         <v>5.2910986084410663</v>
       </c>
       <c r="E172" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F172" s="14">
         <f t="shared" si="64"/>
@@ -8696,7 +8696,7 @@
         <v>8.8184976807351099</v>
       </c>
       <c r="E173" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F173" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="174" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B174" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C174" s="56">
         <v>76</v>
@@ -8758,7 +8758,7 @@
     </row>
     <row r="175" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B175" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C175" s="56">
         <v>135</v>
@@ -8768,7 +8768,7 @@
         <v>4.7619887475969591</v>
       </c>
       <c r="E175" s="25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F175" s="14">
         <f t="shared" si="64"/>
@@ -8794,7 +8794,7 @@
     </row>
     <row r="176" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B176" s="43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C176" s="56">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="E176" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F176" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="D177" s="21"/>
       <c r="E177" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F177" s="14"/>
       <c r="G177" s="81"/>
@@ -8863,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F178" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8889,7 +8889,7 @@
     </row>
     <row r="179" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B179" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C179" s="99">
         <f>SUMIF(B166:B178,"x",C166:C178)</f>
@@ -8900,7 +8900,7 @@
         <v>35.485634667278084</v>
       </c>
       <c r="E179" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F179" s="14">
         <f t="shared" si="64"/>
@@ -8922,7 +8922,7 @@
     </row>
     <row r="180" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B180" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C180" s="56"/>
       <c r="D180" s="21" t="str">
@@ -8930,7 +8930,7 @@
         <v/>
       </c>
       <c r="E180" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F180" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="181" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B181" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C181" s="56"/>
       <c r="D181" s="21" t="str">
@@ -8960,7 +8960,7 @@
         <v/>
       </c>
       <c r="E181" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F181" s="14" t="str">
         <f t="shared" si="64"/>
@@ -8982,7 +8982,7 @@
     </row>
     <row r="182" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B182" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C182" s="56"/>
       <c r="D182" s="21" t="str">
@@ -8990,7 +8990,7 @@
         <v/>
       </c>
       <c r="E182" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F182" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="183" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B183" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C183" s="56"/>
       <c r="D183" s="21" t="str">
@@ -9020,7 +9020,7 @@
         <v/>
       </c>
       <c r="E183" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F183" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9048,7 +9048,7 @@
         <v/>
       </c>
       <c r="E184" s="25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F184" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9073,7 +9073,7 @@
       <c r="C185" s="56"/>
       <c r="D185" s="21"/>
       <c r="E185" s="42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F185" s="14"/>
       <c r="G185" s="14"/>
@@ -9095,7 +9095,7 @@
         <v/>
       </c>
       <c r="E186" s="42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F186" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9123,7 +9123,7 @@
         <v/>
       </c>
       <c r="E187" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F187" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="189" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B189" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C189" s="56"/>
       <c r="D189" s="21" t="str">
@@ -9178,7 +9178,7 @@
         <v/>
       </c>
       <c r="E189" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F189" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9200,7 +9200,7 @@
     </row>
     <row r="190" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B190" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C190" s="56"/>
       <c r="D190" s="21" t="str">
@@ -9208,7 +9208,7 @@
         <v/>
       </c>
       <c r="E190" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F190" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="191" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B191" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C191" s="56"/>
       <c r="D191" s="21" t="str">
@@ -9238,7 +9238,7 @@
         <v/>
       </c>
       <c r="E191" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F191" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9260,7 +9260,7 @@
     </row>
     <row r="192" spans="2:14" ht="15" x14ac:dyDescent="0.25">
       <c r="B192" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C192" s="56"/>
       <c r="D192" s="21" t="str">
@@ -9268,7 +9268,7 @@
         <v/>
       </c>
       <c r="E192" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F192" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9290,7 +9290,7 @@
     </row>
     <row r="193" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B193" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C193" s="56"/>
       <c r="D193" s="21" t="str">
@@ -9320,7 +9320,7 @@
     </row>
     <row r="194" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B194" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C194" s="56"/>
       <c r="D194" s="21" t="str">
@@ -9350,7 +9350,7 @@
     </row>
     <row r="195" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B195" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C195" s="56"/>
       <c r="D195" s="21" t="str">
@@ -9358,7 +9358,7 @@
         <v/>
       </c>
       <c r="E195" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F195" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9380,7 +9380,7 @@
     </row>
     <row r="196" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B196" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C196" s="56"/>
       <c r="D196" s="21" t="str">
@@ -9388,7 +9388,7 @@
         <v/>
       </c>
       <c r="E196" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F196" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9410,7 +9410,7 @@
     </row>
     <row r="197" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B197" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C197" s="56"/>
       <c r="D197" s="21" t="str">
@@ -9440,7 +9440,7 @@
     </row>
     <row r="198" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B198" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C198" s="56"/>
       <c r="D198" s="21" t="str">
@@ -9448,7 +9448,7 @@
         <v/>
       </c>
       <c r="E198" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F198" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="199" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B199" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C199" s="56"/>
       <c r="D199" s="21" t="str">
@@ -9500,7 +9500,7 @@
     </row>
     <row r="200" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B200" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C200" s="56"/>
       <c r="D200" s="21" t="str">
@@ -9508,7 +9508,7 @@
         <v/>
       </c>
       <c r="E200" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F200" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="201" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B201" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C201" s="56"/>
       <c r="D201" s="21" t="str">
@@ -9560,7 +9560,7 @@
     </row>
     <row r="202" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B202" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C202" s="56"/>
       <c r="D202" s="21" t="str">
@@ -9568,7 +9568,7 @@
         <v/>
       </c>
       <c r="E202" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F202" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9590,7 +9590,7 @@
     </row>
     <row r="203" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B203" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C203" s="56"/>
       <c r="D203" s="21" t="str">
@@ -9598,7 +9598,7 @@
         <v/>
       </c>
       <c r="E203" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F203" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9620,7 +9620,7 @@
     </row>
     <row r="204" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B204" s="25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C204" s="56"/>
       <c r="D204" s="21" t="str">
@@ -9650,7 +9650,7 @@
     </row>
     <row r="205" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B205" s="25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C205" s="56"/>
       <c r="D205" s="21" t="str">
@@ -9658,7 +9658,7 @@
         <v/>
       </c>
       <c r="E205" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F205" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="206" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B206" s="111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C206" s="112"/>
       <c r="D206" s="21" t="str">
@@ -9688,7 +9688,7 @@
         <v/>
       </c>
       <c r="E206" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F206" s="14" t="str">
         <f t="shared" si="64"/>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="208" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="124" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C208" s="56"/>
       <c r="D208" s="21"/>
@@ -9748,10 +9748,10 @@
         <v>752.11203019453603</v>
       </c>
       <c r="E209" s="65" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F209" s="63" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G209" s="64" t="s">
         <v>1</v>
@@ -9768,7 +9768,7 @@
         <v>21322</v>
       </c>
       <c r="E210" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F210" s="5">
         <f>TRUNC(D210/D211/16)</f>
@@ -9781,7 +9781,7 @@
       <c r="H210" s="93"/>
       <c r="I210" s="28"/>
       <c r="J210" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="211" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9791,7 +9791,7 @@
         <v>28.349499999999999</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F211" s="62">
         <v>7</v>
@@ -9802,7 +9802,7 @@
       <c r="H211" s="94"/>
       <c r="I211" s="22"/>
       <c r="J211" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="212" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9812,7 +9812,7 @@
         <v>3.5274E-2</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F212" s="23">
         <v>4</v>
@@ -9821,7 +9821,7 @@
       <c r="H212" s="95"/>
       <c r="I212" s="24"/>
       <c r="J212" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="213" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9829,7 +9829,7 @@
       <c r="C213" s="77"/>
       <c r="D213" s="20"/>
       <c r="E213" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F213" s="4">
         <f>SUM(F210:F212)</f>
@@ -9842,7 +9842,7 @@
       <c r="H213" s="93"/>
       <c r="I213" s="28"/>
       <c r="J213" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="214" spans="2:10" ht="15" x14ac:dyDescent="0.25">
@@ -9850,7 +9850,7 @@
       <c r="C214" s="77"/>
       <c r="D214" s="20"/>
       <c r="E214" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F214" s="20"/>
       <c r="G214" s="20"/>
@@ -9862,10 +9862,10 @@
       <c r="B215" s="18"/>
       <c r="C215" s="77"/>
       <c r="D215" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E215" s="20" t="s">
         <v>29</v>
-      </c>
-      <c r="E215" s="20" t="s">
-        <v>30</v>
       </c>
       <c r="G215" s="20"/>
       <c r="H215" s="89"/>
@@ -9969,10 +9969,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12">
-    <cfRule type="containsText" dxfId="1" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
+    <cfRule type="containsText" dxfId="5" priority="1" stopIfTrue="1" operator="containsText" text="~*~*">
       <formula>NOT(ISERROR(SEARCH("~*~*",N12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="~*">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="~*">
       <formula>NOT(ISERROR(SEARCH("~*",N12)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10040,25 +10040,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2" t="str">
         <v>Blue Pack</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D2" t="str">
         <v>pot .7 gt cup &amp; windscreen</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F2" t="str">
         <v>Maps</v>
       </c>
       <c r="G2" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H2" t="str">
         <v>Medication</v>
@@ -10066,25 +10066,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" t="str">
         <v>Pack hip pockets</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D3" t="str">
         <v>IsoPro Stove w/ ignitor</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F3" t="str">
         <v>Compass</v>
       </c>
       <c r="G3" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H3" t="str">
         <v>24-32 ounces food per day</v>
@@ -10092,25 +10092,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" t="str">
         <v>Pack Liner/Garbage bag</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D4" t="str">
         <v>IsoPro canister 8oz</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F4" t="str">
         <v>Trail details</v>
       </c>
       <c r="G4" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H4" t="str">
         <v>64 ounces water</v>
@@ -10118,19 +10118,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B5" t="str">
         <v>Orange Pack Cover</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D5" t="str">
         <v>IsoPro canister stand</v>
       </c>
       <c r="E5" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F5" t="str">
         <v>pen / pencil</v>
@@ -10144,13 +10144,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D6" t="str">
         <v>cozy for freezer bag meals</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F6" t="str">
         <v>notepad / journal</v>
@@ -10165,7 +10165,7 @@
         <v>Shelter Group</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" t="str">
         <v>lighter</v>
@@ -10175,7 +10175,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G7" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H7" t="str">
         <v>trekking poles</v>
@@ -10183,13 +10183,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B8" t="str">
         <v>Bridge Hammock; 1.2 Hexon Olive</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" t="str">
         <v>spork short</v>
@@ -10199,7 +10199,7 @@
         <v>First Aid Group</v>
       </c>
       <c r="G8" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H8" t="str">
         <v>hiking boots</v>
@@ -10207,25 +10207,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B9" t="str">
         <v>Spreader Bars 28"</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D9" t="str">
         <v>spoon long</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F9" t="str">
         <v>First aid kit</v>
       </c>
       <c r="G9" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H9" t="str">
         <v>liner socks</v>
@@ -10233,13 +10233,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" t="str">
         <v>Tree straps spider poly</v>
       </c>
       <c r="C10" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="str">
         <v>3 liter bladder</v>
@@ -10249,7 +10249,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G10" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" t="str">
         <v>wool socks</v>
@@ -10257,13 +10257,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B11" t="str">
         <v>UCR</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D11" t="str">
         <v>water bottles collapsable</v>
@@ -10273,7 +10273,7 @@
         <v>Repair Group</v>
       </c>
       <c r="G11" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H11" t="str">
         <v>gators</v>
@@ -10281,25 +10281,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" t="str">
         <v>Tarp Forest green &amp; lines</v>
       </c>
       <c r="C12" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D12" t="str">
         <v>smart water bottles</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F12" t="str">
         <v>Tenacious tape</v>
       </c>
       <c r="G12" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H12" t="str">
         <v>tech shirt</v>
@@ -10307,25 +10307,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B13" t="str">
         <v>stakes AL red</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D13" t="str">
         <v>Water Filter Kit</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F13" t="str">
         <v>Duct tape on trekking poles</v>
       </c>
       <c r="G13" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H13" t="str">
         <v>underwear</v>
@@ -10333,25 +10333,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B14" t="str">
         <v>Tyvek 4x3</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D14" t="str">
         <v xml:space="preserve">  --Filter  (New: Versa Filter)</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F14" t="str">
         <v>extra buckle</v>
       </c>
       <c r="G14" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H14" t="str">
         <v>Kilt / Zip-offs</v>
@@ -10359,13 +10359,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B15" t="str">
         <v>Mylar blanket</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D15" t="str">
         <v xml:space="preserve">   --CNOC 3 liter</v>
@@ -10375,7 +10375,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="G15" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H15" t="str">
         <v>runners cap</v>
@@ -10386,7 +10386,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D16" t="str">
         <v xml:space="preserve">  --tubing</v>
@@ -10396,7 +10396,7 @@
         <v>Misc Group</v>
       </c>
       <c r="G16" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H16" t="str">
         <v>pocket knife</v>
@@ -10407,19 +10407,19 @@
         <v>Sleeping Group</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D17" t="str">
         <v xml:space="preserve">  --sawyer squeze</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F17" t="str">
         <v>phone battery 4,000mAh</v>
       </c>
       <c r="G17" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H17" t="str">
         <v>lip balm</v>
@@ -10427,25 +10427,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B18" t="str">
         <v>15° sleeping bag - Katahdin</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D18" t="str">
         <v xml:space="preserve">  --bleach/polar pure/ tablets</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F18" t="str">
         <v>Camp chair - heavy</v>
       </c>
       <c r="G18" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H18" t="str">
         <v>phone (in zip-loc)</v>
@@ -10453,25 +10453,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B19" t="str">
         <v>sleeping bag liner blue</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D19" t="str">
         <v>food bag Blue</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F19" t="str">
         <v>hammock chair (green)</v>
       </c>
       <c r="G19" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H19" t="str">
         <v>license / money / credit card</v>
@@ -10479,25 +10479,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B20" t="str">
         <v>pillow black (Outdoor Vitals)</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D20" t="str">
-        <v>bear bag and rope</v>
+        <v>bag and rope</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F20" t="str">
         <v>head lamp</v>
       </c>
       <c r="G20" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H20" t="str">
         <v>bandana</v>
@@ -10505,25 +10505,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B21" t="str">
         <v>Under Quilt Blue 5.0 Climashield</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D21" t="str">
         <v>red bandana</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F21" t="str">
         <v>spare batteries 3 AAA</v>
       </c>
       <c r="G21" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H21" t="str">
         <v>belt</v>
@@ -10531,7 +10531,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B22" t="str">
         <v xml:space="preserve"> </v>
@@ -10541,13 +10541,13 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F22" t="str">
         <v>rope pieces</v>
       </c>
       <c r="G22" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H22" t="str">
         <v>suspenders</v>
@@ -10563,7 +10563,7 @@
         <v>Hygiene Group</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F23" t="str">
         <v>eye glass case - soft</v>
@@ -10575,13 +10575,13 @@
         <v>Down booties</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D24" t="str">
         <v>Bathroom kit</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F24" t="str">
         <v>foam pad 12 x 18</v>
@@ -10589,13 +10589,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" t="str">
         <v>Fleece hat</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D25" t="str">
         <v xml:space="preserve">  --TP</v>
@@ -10607,13 +10607,13 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B26" t="str">
         <v>long sleeve shirt</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D26" t="str">
         <v xml:space="preserve">  --wet wipes</v>
@@ -10625,19 +10625,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B27" t="str">
         <v>underwear</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D27" t="str">
         <v xml:space="preserve">  -- hand sanitizer</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F27" t="str">
         <v>puffy</v>
@@ -10645,19 +10645,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28" t="str">
         <v>Wool socks</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D28" t="str">
         <v xml:space="preserve">  --Gold Bond</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F28" t="str">
         <v>gloves/mittens</v>
@@ -10665,19 +10665,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B29" t="str">
         <v>Liner socks</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D29" t="str">
         <v>Shovel plastic</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F29" t="str">
         <v>Liner socks</v>
@@ -10685,19 +10685,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B30" t="str">
         <v>running tights *</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D30" t="str">
         <v>water jug botom</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F30" t="str">
         <v>Wool socks</v>
@@ -10705,19 +10705,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B31" t="str">
         <v>camp shoes</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D31" t="str">
         <v>tooth brush</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F31" t="str">
         <v xml:space="preserve">long sleeve shirt </v>
@@ -10725,19 +10725,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B32" t="str">
         <v xml:space="preserve"> </v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D32" t="str">
         <v>tooth  dots / paste</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F32" t="str">
         <v>underwear</v>
@@ -10748,13 +10748,13 @@
         <v>Rain Gear Group</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D33" t="str">
         <v>hand sanitizer on pack</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F33" t="str">
         <v>shorts</v>
@@ -10769,7 +10769,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F34" t="str">
         <v>zip-offs</v>
@@ -10777,7 +10777,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B35" t="str">
         <v>Rain pants blue FroggTog</v>
@@ -10789,7 +10789,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="68" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B36" t="str">
         <v xml:space="preserve"> </v>
@@ -10797,13 +10797,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:H15 B16:H18 A18 A19:H31 A32 B32:H33 A34:H44">
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Pounds">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Pounds">
       <formula>NOT(ISERROR(SEARCH("Pounds",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="Ounces">
+    <cfRule type="containsText" dxfId="2" priority="8" operator="containsText" text="Ounces">
       <formula>NOT(ISERROR(SEARCH("Ounces",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11718,7 +11718,7 @@
         <v>1.1287677031340941</v>
       </c>
       <c r="C56" t="str">
-        <v>bear bag and rope</v>
+        <v>bag and rope</v>
       </c>
       <c r="D56" s="109">
         <v>0</v>
@@ -12819,7 +12819,7 @@
         <v>758.24970458032828</v>
       </c>
       <c r="C131" s="69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D131" s="110"/>
       <c r="E131" s="107"/>
@@ -12835,7 +12835,7 @@
         <v>47</v>
       </c>
       <c r="C132" s="70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D132" s="110"/>
       <c r="E132" s="107"/>
@@ -12850,7 +12850,7 @@
         <v>6.2497045803282845</v>
       </c>
       <c r="C133" s="71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D133" s="110"/>
       <c r="E133" s="107"/>
@@ -12859,7 +12859,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:G124 C131:G151">
-    <cfRule type="containsText" dxfId="2" priority="13" operator="containsText" text="Group">
+    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="Group">
       <formula>NOT(ISERROR(SEARCH("Group",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12891,10 +12891,10 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>1</v>
@@ -12903,7 +12903,7 @@
         <v>28.349499999999999</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12924,7 +12924,7 @@
         <v>3.5274E-2</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -12945,7 +12945,7 @@
         <v>1296</v>
       </c>
       <c r="H3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -12995,10 +12995,10 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -13010,16 +13010,16 @@
         <v>1</v>
       </c>
       <c r="H8" s="85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I8" s="113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J8" s="113" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="123" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -13044,7 +13044,7 @@
         <v>25.53836928340888</v>
       </c>
       <c r="H9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I9">
         <f>INT(G9/16)</f>
@@ -13063,7 +13063,7 @@
         <v>10.666666666666668</v>
       </c>
       <c r="N9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -13080,7 +13080,7 @@
         <v>7.3017160796486715</v>
       </c>
       <c r="E10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F10">
         <v>193</v>
@@ -13090,7 +13090,7 @@
         <v>6.8078802095275055</v>
       </c>
       <c r="H10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I10">
         <f>INT(G10/16)</f>
@@ -13108,7 +13108,7 @@
         <v>4.0200000000000005</v>
       </c>
       <c r="N10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13132,7 +13132,7 @@
         <v>10.688019189050953</v>
       </c>
       <c r="H11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I11">
         <f>INT(G11/16)</f>
@@ -13168,7 +13168,7 @@
         <v>0.3527399072294044</v>
       </c>
       <c r="H12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I12">
         <f>INT(G12/16)</f>
@@ -13193,7 +13193,7 @@
         <v>10.970211114834477</v>
       </c>
       <c r="E13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F13">
         <v>37</v>
@@ -13203,7 +13203,7 @@
         <v>1.3051376567487962</v>
       </c>
       <c r="H13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I13">
         <f>INT(G13/16)</f>
@@ -13253,10 +13253,10 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C17" s="86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>1</v>
@@ -13286,7 +13286,7 @@
         <v>17.284255454240817</v>
       </c>
       <c r="H18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I18">
         <f>INT(G18/16)</f>
@@ -13339,7 +13339,7 @@
         <v>61.976401700206353</v>
       </c>
       <c r="H21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I21">
         <f>INT(G21/16)</f>
@@ -13352,10 +13352,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C22" s="86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>1</v>
@@ -13461,12 +13461,12 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F30" t="s">
         <v>0</v>
@@ -13475,16 +13475,16 @@
         <v>1</v>
       </c>
       <c r="I30" s="113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J30" s="113" t="s">
         <v>1</v>
       </c>
       <c r="M30" t="s">
+        <v>247</v>
+      </c>
+      <c r="O30" t="s">
         <v>248</v>
-      </c>
-      <c r="O30" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="J31" s="9"/>
       <c r="L31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M31">
         <v>0.9</v>
@@ -13540,7 +13540,7 @@
         <v>28.166666666666664</v>
       </c>
       <c r="H32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I32">
         <f t="shared" ref="I32:I33" si="0">INT(G32/16)</f>
@@ -13593,7 +13593,7 @@
         <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I33">
         <f t="shared" si="0"/>
@@ -13646,7 +13646,7 @@
         <v>54.166666666666664</v>
       </c>
       <c r="H34" s="116" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I34" s="116">
         <f>SUM(I32:I33)</f>
@@ -13678,7 +13678,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="H35" s="117" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I35" s="117">
         <f>INT(G35/16)</f>
@@ -13689,7 +13689,7 @@
         <v>4.5150708125363765</v>
       </c>
       <c r="K35" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -13711,7 +13711,7 @@
         <v>1.6931515547011413</v>
       </c>
       <c r="H36" s="120" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I36" s="120">
         <f>INT(G36/16)</f>
@@ -13755,7 +13755,7 @@
         <v>22.313333333333325</v>
       </c>
       <c r="H38" s="122" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I38" s="122">
         <f t="shared" ref="I38" si="3">INT(G38/16)</f>
@@ -13766,7 +13766,7 @@
         <v>6.3133333333333255</v>
       </c>
       <c r="L38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -13786,7 +13786,7 @@
         <v>2</v>
       </c>
       <c r="M39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -13806,7 +13806,7 @@
         <v>3.6</v>
       </c>
       <c r="M40" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -13826,7 +13826,7 @@
         <v>5</v>
       </c>
       <c r="M41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -13846,7 +13846,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -13866,7 +13866,7 @@
         <v>7.5</v>
       </c>
       <c r="M43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -13875,7 +13875,7 @@
         <v>76.47999999999999</v>
       </c>
       <c r="B45" s="116" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C45" s="116">
         <f t="shared" ref="C45" si="5">INT(A45/16)</f>

--- a/AT/GearListNew.xlsx
+++ b/AT/GearListNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1195" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B575C0-2620-4F9F-A622-B5A716DA572C}"/>
+  <xr:revisionPtr revIDLastSave="1202" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046DF09D-8FF9-4618-A890-E4921C5BA11D}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="855" windowWidth="27525" windowHeight="15225" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12630" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gear Checklist" sheetId="6" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="273">
   <si>
     <t>gm</t>
   </si>
@@ -961,6 +961,9 @@
   </si>
   <si>
     <t>bag and rope</t>
+  </si>
+  <si>
+    <t>New Gathered end hammock  with bug net</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="74" t="str">
-        <v>bug net new</v>
+        <v>New Gathered end hammock  with bug net</v>
       </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
@@ -2414,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="74" t="str">
-        <v>sleeping bag liner #2</v>
+        <v>bug net new</v>
       </c>
       <c r="K8" s="20"/>
       <c r="L8" s="20"/>
@@ -2468,7 +2471,7 @@
         <v>0.95239774951939193</v>
       </c>
       <c r="J9" s="74" t="str">
-        <v>Top Quilt</v>
+        <v>sleeping bag liner #2</v>
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
@@ -2522,7 +2525,7 @@
         <v>5.0441806733804828</v>
       </c>
       <c r="J10" s="74" t="str">
-        <v>New Under Quilt</v>
+        <v>Top Quilt</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
@@ -2571,7 +2574,7 @@
         <v>7.0547981445880881</v>
       </c>
       <c r="J11" s="74" t="str">
-        <v>New Rain Pants Xeon</v>
+        <v>New Under Quilt</v>
       </c>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
@@ -2618,7 +2621,7 @@
         <v>5.1500026455493044</v>
       </c>
       <c r="J12" s="74" t="str">
-        <v>BRS 3000T Stove</v>
+        <v>New Rain Pants Xeon</v>
       </c>
       <c r="K12" s="20"/>
       <c r="L12" s="20"/>
@@ -2888,7 +2891,9 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E19" s="83"/>
+      <c r="E19" s="83" t="s">
+        <v>272</v>
+      </c>
       <c r="F19" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -2906,7 +2911,9 @@
         <v/>
       </c>
       <c r="J19" s="25"/>
-      <c r="K19" s="20"/>
+      <c r="K19" s="20" t="s">
+        <v>41</v>
+      </c>
       <c r="L19" s="20"/>
       <c r="M19" s="21"/>
       <c r="N19" s="25"/>
@@ -5518,9 +5525,7 @@
       <c r="T82" s="25"/>
     </row>
     <row r="83" spans="2:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="B83" s="18" t="s">
-        <v>41</v>
-      </c>
+      <c r="B83" s="18"/>
       <c r="C83" s="56">
         <v>110</v>
       </c>
@@ -5531,13 +5536,13 @@
       <c r="E83" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="F83" s="14">
+      <c r="F83" s="14" t="str">
         <f t="shared" si="37"/>
-        <v>110</v>
-      </c>
-      <c r="G83" s="81">
+        <v/>
+      </c>
+      <c r="G83" s="81" t="str">
         <f t="shared" si="38"/>
-        <v>3.8801389795234487</v>
+        <v/>
       </c>
       <c r="H83" s="89">
         <f t="shared" si="31"/>
@@ -5560,7 +5565,9 @@
       <c r="T83" s="25"/>
     </row>
     <row r="84" spans="2:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="B84" s="18"/>
+      <c r="B84" s="124" t="s">
+        <v>41</v>
+      </c>
       <c r="C84" s="56">
         <v>25</v>
       </c>
@@ -5571,13 +5578,13 @@
       <c r="E84" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="F84" s="14" t="str">
+      <c r="F84" s="14">
         <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="G84" s="81" t="str">
+        <v>25</v>
+      </c>
+      <c r="G84" s="81">
         <f t="shared" si="38"/>
-        <v/>
+        <v>0.88184976807351101</v>
       </c>
       <c r="H84" s="89">
         <f t="shared" si="31"/>
@@ -5590,9 +5597,7 @@
       <c r="J84" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="K84" s="20" t="s">
-        <v>41</v>
-      </c>
+      <c r="K84" s="20"/>
       <c r="L84" s="20"/>
       <c r="M84" s="21"/>
       <c r="N84" s="25"/>
@@ -6589,11 +6594,11 @@
       <c r="B109" s="18"/>
       <c r="C109" s="99">
         <f>SUMIF(B81:B108,"x",C81:C108)</f>
-        <v>1172</v>
+        <v>1087</v>
       </c>
       <c r="D109" s="21">
         <f t="shared" si="48"/>
-        <v>41.341117127286196</v>
+        <v>38.34282791583626</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>40</v>
@@ -6612,7 +6617,7 @@
       </c>
       <c r="I109" s="21">
         <f t="shared" si="32"/>
-        <v>9.3411171272861964</v>
+        <v>6.3428279158362599</v>
       </c>
       <c r="J109" s="25"/>
       <c r="K109" s="37"/>
@@ -9741,11 +9746,11 @@
       <c r="B209" s="18"/>
       <c r="C209" s="78">
         <f>SUM(F2:F208)</f>
-        <v>21322</v>
+        <v>21237</v>
       </c>
       <c r="D209" s="39">
         <f>IF(ISBLANK(C209),"", C209/$D$211)</f>
-        <v>752.11203019453603</v>
+        <v>749.11374098308613</v>
       </c>
       <c r="E209" s="65" t="s">
         <v>169</v>
@@ -9765,18 +9770,18 @@
       <c r="C210" s="77"/>
       <c r="D210" s="8">
         <f>C209</f>
-        <v>21322</v>
+        <v>21237</v>
       </c>
       <c r="E210" s="34" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="5">
         <f>TRUNC(D210/D211/16)</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G210" s="28">
         <f>(D210/D211/16-TRUNC(D210/D211/16))*16</f>
-        <v>0.11203019453603247</v>
+        <v>13.113740983086132</v>
       </c>
       <c r="H210" s="93"/>
       <c r="I210" s="28"/>
@@ -9833,11 +9838,11 @@
       </c>
       <c r="F213" s="4">
         <f>SUM(F210:F212)</f>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G213" s="28">
         <f>SUM(G210:G212)</f>
-        <v>8.1120301945360325</v>
+        <v>21.113740983086132</v>
       </c>
       <c r="H213" s="93"/>
       <c r="I213" s="28"/>
@@ -9976,7 +9981,7 @@
       <formula>NOT(ISERROR(SEARCH("~*",N12)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="7">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N4" xr:uid="{93D0D4FF-F73B-4CEC-9F59-1E03B78731B5}">
       <formula1>Backpacks</formula1>
     </dataValidation>
@@ -10075,7 +10080,7 @@
         <v>180</v>
       </c>
       <c r="D3" t="str">
-        <v>IsoPro Stove w/ ignitor</v>
+        <v>BRS 3000T Stove</v>
       </c>
       <c r="E3" s="68" t="s">
         <v>180</v>
@@ -11443,16 +11448,16 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="101">
-        <v>3.8801389795234487</v>
+        <v>0.88184976807351101</v>
       </c>
       <c r="C39" t="str">
-        <v>IsoPro Stove w/ ignitor</v>
+        <v>BRS 3000T Stove</v>
       </c>
       <c r="D39" s="109">
         <v>0</v>
       </c>
       <c r="E39" s="106">
-        <v>3.8801389795234487</v>
+        <v>0.88184976807351101</v>
       </c>
       <c r="I39" s="86"/>
       <c r="J39" s="84"/>
@@ -12816,7 +12821,7 @@
     <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="102">
         <f>SUM(B1:B127)</f>
-        <v>758.24970458032828</v>
+        <v>755.25141536887827</v>
       </c>
       <c r="C131" s="69" t="s">
         <v>181</v>
@@ -12847,7 +12852,7 @@
     <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="104">
         <f>MOD(B131,16)</f>
-        <v>6.2497045803282845</v>
+        <v>3.2514153688782699</v>
       </c>
       <c r="C133" s="71" t="s">
         <v>167</v>

--- a/AT/GearListNew.xlsx
+++ b/AT/GearListNew.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1202" documentId="8_{1551697D-00C6-4CE6-A106-D804D9434B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046DF09D-8FF9-4618-A890-E4921C5BA11D}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12630" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
+    <workbookView xWindow="3465" yWindow="1395" windowWidth="21600" windowHeight="14250" xr2:uid="{68AAFF99-797A-4764-8C30-A0E86570531C}"/>
   </bookViews>
   <sheets>
     <sheet name="New Gear Checklist" sheetId="6" r:id="rId1"/>
